--- a/WORK/Projects_HAESL/proj_digital_streamer/assets/map_UAT_streamer_20260415/file-20260415112851687.xlsx
+++ b/WORK/Projects_HAESL/proj_digital_streamer/assets/map_UAT_streamer_20260415/file-20260415112851687.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="V:\Customer &amp; Planning\Business Support\VBA Improvement\projects\UAT - HAESL Digital Streamer\test cases\[test-cases] Test Slot Plan Upload\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yk-chris.chan\Documents\GitHub\Obsidian_2nd_brain\WORK\Projects_HAESL\proj_digital_streamer\assets\map_UAT_streamer_20260415\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2D593F6-5E6C-4228-A872-C79FF453837F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F48C5853-DF03-4BA9-B41E-250464486726}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{59FB7277-34E1-4CA7-B3F3-92087669BE89}"/>
   </bookViews>
@@ -1040,7 +1040,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
@@ -1105,8 +1105,7 @@
     <xf numFmtId="15" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
@@ -1119,7 +1118,6 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="15" fontId="4" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
@@ -2581,6 +2579,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B650FDFD-1E0B-475B-B19D-CB053650987F}">
+  <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:J58"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2590,8 +2589,8 @@
     <col min="4" max="5" width="16.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15.85546875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11.28515625" style="13" customWidth="1"/>
-    <col min="8" max="8" width="10.5703125" style="22" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="11.85546875" style="22" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="11.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -2616,13 +2615,13 @@
       <c r="G1" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="H1" s="22" t="s">
+      <c r="H1" t="s">
         <v>110</v>
       </c>
-      <c r="I1" s="22" t="s">
+      <c r="I1" t="s">
         <v>111</v>
       </c>
-      <c r="J1" s="22" t="s">
+      <c r="J1" t="s">
         <v>112</v>
       </c>
     </row>
@@ -2643,15 +2642,15 @@
         <v>46089</v>
       </c>
       <c r="F2" s="20"/>
-      <c r="H2" s="22">
+      <c r="H2">
         <f>D2-VLOOKUP(A2,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I2" s="22">
+      <c r="I2">
         <f>E2-VLOOKUP(A2,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J2" s="22">
+      <c r="J2">
         <f>F2-VLOOKUP(A2,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -2673,15 +2672,15 @@
         <v>46094</v>
       </c>
       <c r="F3" s="5"/>
-      <c r="H3" s="22">
+      <c r="H3">
         <f>D3-VLOOKUP(A3,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I3" s="22">
+      <c r="I3">
         <f>E3-VLOOKUP(A3,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J3" s="22">
+      <c r="J3">
         <f>F3-VLOOKUP(A3,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -2708,15 +2707,15 @@
       <c r="G4" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="H4" s="22">
+      <c r="H4">
         <f>D4-VLOOKUP(A4,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I4" s="22">
+      <c r="I4">
         <f>E4-VLOOKUP(A4,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J4" s="22">
+      <c r="J4">
         <f>F4-VLOOKUP(A4,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -2738,15 +2737,15 @@
         <v>46103</v>
       </c>
       <c r="F5" s="5"/>
-      <c r="H5" s="22">
+      <c r="H5">
         <f>D5-VLOOKUP(A5,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I5" s="22">
+      <c r="I5">
         <f>E5-VLOOKUP(A5,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J5" s="22">
+      <c r="J5">
         <f>F5-VLOOKUP(A5,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -2768,15 +2767,15 @@
         <v>46107</v>
       </c>
       <c r="F6" s="5"/>
-      <c r="H6" s="22">
+      <c r="H6">
         <f>D6-VLOOKUP(A6,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I6" s="22">
+      <c r="I6">
         <f>E6-VLOOKUP(A6,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J6" s="22">
+      <c r="J6">
         <f>F6-VLOOKUP(A6,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -2798,15 +2797,15 @@
         <v>46114</v>
       </c>
       <c r="F7" s="5"/>
-      <c r="H7" s="22">
+      <c r="H7">
         <f>D7-VLOOKUP(A7,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I7" s="22">
+      <c r="I7">
         <f>E7-VLOOKUP(A7,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J7" s="22">
+      <c r="J7">
         <f>F7-VLOOKUP(A7,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -2828,15 +2827,15 @@
         <v>46109</v>
       </c>
       <c r="F8" s="5"/>
-      <c r="H8" s="22">
+      <c r="H8">
         <f>D8-VLOOKUP(A8,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I8" s="22">
+      <c r="I8">
         <f>E8-VLOOKUP(A8,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J8" s="22">
+      <c r="J8">
         <f>F8-VLOOKUP(A8,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -2858,15 +2857,15 @@
         <v>46109</v>
       </c>
       <c r="F9" s="5"/>
-      <c r="H9" s="22">
+      <c r="H9">
         <f>D9-VLOOKUP(A9,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I9" s="22">
+      <c r="I9">
         <f>E9-VLOOKUP(A9,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J9" s="22">
+      <c r="J9">
         <f>F9-VLOOKUP(A9,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -2888,15 +2887,15 @@
         <v>46109</v>
       </c>
       <c r="F10" s="5"/>
-      <c r="H10" s="22">
+      <c r="H10">
         <f>D10-VLOOKUP(A10,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I10" s="22">
+      <c r="I10">
         <f>E10-VLOOKUP(A10,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J10" s="22">
+      <c r="J10">
         <f>F10-VLOOKUP(A10,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -2918,15 +2917,15 @@
         <v>46109</v>
       </c>
       <c r="F11" s="5"/>
-      <c r="H11" s="22">
+      <c r="H11">
         <f>D11-VLOOKUP(A11,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I11" s="22">
+      <c r="I11">
         <f>E11-VLOOKUP(A11,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J11" s="22">
+      <c r="J11">
         <f>F11-VLOOKUP(A11,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -2948,15 +2947,15 @@
         <v>46109</v>
       </c>
       <c r="F12" s="5"/>
-      <c r="H12" s="22">
+      <c r="H12">
         <f>D12-VLOOKUP(A12,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I12" s="22">
+      <c r="I12">
         <f>E12-VLOOKUP(A12,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J12" s="22">
+      <c r="J12">
         <f>F12-VLOOKUP(A12,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -2978,15 +2977,15 @@
         <v>46109</v>
       </c>
       <c r="F13" s="5"/>
-      <c r="H13" s="22">
+      <c r="H13">
         <f>D13-VLOOKUP(A13,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I13" s="22">
+      <c r="I13">
         <f>E13-VLOOKUP(A13,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J13" s="22">
+      <c r="J13">
         <f>F13-VLOOKUP(A13,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -3008,15 +3007,15 @@
         <v>46109</v>
       </c>
       <c r="F14" s="5"/>
-      <c r="H14" s="22">
+      <c r="H14">
         <f>D14-VLOOKUP(A14,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I14" s="22">
+      <c r="I14">
         <f>E14-VLOOKUP(A14,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J14" s="22">
+      <c r="J14">
         <f>F14-VLOOKUP(A14,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -3038,15 +3037,15 @@
         <v>46109</v>
       </c>
       <c r="F15" s="5"/>
-      <c r="H15" s="22">
+      <c r="H15">
         <f>D15-VLOOKUP(A15,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I15" s="22">
+      <c r="I15">
         <f>E15-VLOOKUP(A15,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J15" s="22">
+      <c r="J15">
         <f>F15-VLOOKUP(A15,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -3068,15 +3067,15 @@
         <v>46108</v>
       </c>
       <c r="F16" s="5"/>
-      <c r="H16" s="22">
+      <c r="H16">
         <f>D16-VLOOKUP(A16,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I16" s="22">
+      <c r="I16">
         <f>E16-VLOOKUP(A16,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J16" s="22">
+      <c r="J16">
         <f>F16-VLOOKUP(A16,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -3098,15 +3097,15 @@
         <v>46109</v>
       </c>
       <c r="F17" s="5"/>
-      <c r="H17" s="22">
+      <c r="H17">
         <f>D17-VLOOKUP(A17,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I17" s="22">
+      <c r="I17">
         <f>E17-VLOOKUP(A17,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J17" s="22">
+      <c r="J17">
         <f>F17-VLOOKUP(A17,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -3128,15 +3127,15 @@
         <v>46115</v>
       </c>
       <c r="F18" s="5"/>
-      <c r="H18" s="22">
+      <c r="H18">
         <f>D18-VLOOKUP(A18,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I18" s="22">
+      <c r="I18">
         <f>E18-VLOOKUP(A18,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J18" s="22">
+      <c r="J18">
         <f>F18-VLOOKUP(A18,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -3161,15 +3160,15 @@
       <c r="G19" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="H19" s="22">
+      <c r="H19">
         <f>D19-VLOOKUP(A19,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I19" s="22">
+      <c r="I19">
         <f>E19-VLOOKUP(A19,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J19" s="22">
+      <c r="J19">
         <f>F19-VLOOKUP(A19,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -3191,15 +3190,15 @@
         <v>46108</v>
       </c>
       <c r="F20" s="5"/>
-      <c r="H20" s="22">
+      <c r="H20">
         <f>D20-VLOOKUP(A20,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I20" s="22">
+      <c r="I20">
         <f>E20-VLOOKUP(A20,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J20" s="22">
+      <c r="J20">
         <f>F20-VLOOKUP(A20,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -3221,15 +3220,15 @@
         <v>46108</v>
       </c>
       <c r="F21" s="5"/>
-      <c r="H21" s="22">
+      <c r="H21">
         <f>D21-VLOOKUP(A21,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I21" s="22">
+      <c r="I21">
         <f>E21-VLOOKUP(A21,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J21" s="22">
+      <c r="J21">
         <f>F21-VLOOKUP(A21,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -3251,15 +3250,15 @@
         <v>46108</v>
       </c>
       <c r="F22" s="5"/>
-      <c r="H22" s="22">
+      <c r="H22">
         <f>D22-VLOOKUP(A22,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I22" s="22">
+      <c r="I22">
         <f>E22-VLOOKUP(A22,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J22" s="22">
+      <c r="J22">
         <f>F22-VLOOKUP(A22,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -3281,15 +3280,15 @@
         <v>46108</v>
       </c>
       <c r="F23" s="5"/>
-      <c r="H23" s="22">
+      <c r="H23">
         <f>D23-VLOOKUP(A23,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I23" s="22">
+      <c r="I23">
         <f>E23-VLOOKUP(A23,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J23" s="22">
+      <c r="J23">
         <f>F23-VLOOKUP(A23,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -3311,15 +3310,15 @@
         <v>46108</v>
       </c>
       <c r="F24" s="5"/>
-      <c r="H24" s="22">
+      <c r="H24">
         <f>D24-VLOOKUP(A24,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I24" s="22">
+      <c r="I24">
         <f>E24-VLOOKUP(A24,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J24" s="22">
+      <c r="J24">
         <f>F24-VLOOKUP(A24,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -3341,15 +3340,15 @@
         <v>46108</v>
       </c>
       <c r="F25" s="5"/>
-      <c r="H25" s="22">
+      <c r="H25">
         <f>D25-VLOOKUP(A25,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I25" s="22">
+      <c r="I25">
         <f>E25-VLOOKUP(A25,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J25" s="22">
+      <c r="J25">
         <f>F25-VLOOKUP(A25,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -3371,15 +3370,15 @@
         <v>46104</v>
       </c>
       <c r="F26" s="5"/>
-      <c r="H26" s="22">
+      <c r="H26">
         <f>D26-VLOOKUP(A26,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I26" s="22">
+      <c r="I26">
         <f>E26-VLOOKUP(A26,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J26" s="22">
+      <c r="J26">
         <f>F26-VLOOKUP(A26,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -3401,15 +3400,15 @@
         <v>46113</v>
       </c>
       <c r="F27" s="5"/>
-      <c r="H27" s="22">
+      <c r="H27">
         <f>D27-VLOOKUP(A27,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I27" s="22">
+      <c r="I27">
         <f>E27-VLOOKUP(A27,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J27" s="22">
+      <c r="J27">
         <f>F27-VLOOKUP(A27,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -3431,15 +3430,15 @@
         <v>46114</v>
       </c>
       <c r="F28" s="5"/>
-      <c r="H28" s="22">
+      <c r="H28">
         <f>D28-VLOOKUP(A28,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I28" s="22">
+      <c r="I28">
         <f>E28-VLOOKUP(A28,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J28" s="22">
+      <c r="J28">
         <f>F28-VLOOKUP(A28,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -3461,15 +3460,15 @@
         <v>46118</v>
       </c>
       <c r="F29" s="5"/>
-      <c r="H29" s="22">
+      <c r="H29">
         <f>D29-VLOOKUP(A29,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I29" s="22">
+      <c r="I29">
         <f>E29-VLOOKUP(A29,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J29" s="22">
+      <c r="J29">
         <f>F29-VLOOKUP(A29,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -3491,15 +3490,15 @@
         <v>46124</v>
       </c>
       <c r="F30" s="5"/>
-      <c r="H30" s="22">
+      <c r="H30">
         <f>D30-VLOOKUP(A30,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I30" s="22">
+      <c r="I30">
         <f>E30-VLOOKUP(A30,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J30" s="22">
+      <c r="J30">
         <f>F30-VLOOKUP(A30,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -3521,15 +3520,15 @@
         <v>46137</v>
       </c>
       <c r="F31" s="5"/>
-      <c r="H31" s="22">
+      <c r="H31">
         <f>D31-VLOOKUP(A31,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I31" s="22">
+      <c r="I31">
         <f>E31-VLOOKUP(A31,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J31" s="22">
+      <c r="J31">
         <f>F31-VLOOKUP(A31,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -3554,15 +3553,15 @@
       <c r="G32" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="H32" s="22">
+      <c r="H32">
         <f>D32-VLOOKUP(A32,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I32" s="22">
+      <c r="I32">
         <f>E32-VLOOKUP(A32,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J32" s="22">
+      <c r="J32">
         <f>F32-VLOOKUP(A32,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -3587,15 +3586,15 @@
       <c r="G33" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="H33" s="22">
+      <c r="H33">
         <f>D33-VLOOKUP(A33,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I33" s="22">
+      <c r="I33">
         <f>E33-VLOOKUP(A33,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J33" s="22">
+      <c r="J33">
         <f>F33-VLOOKUP(A33,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -3620,15 +3619,15 @@
       <c r="G34" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="H34" s="22">
+      <c r="H34">
         <f>D34-VLOOKUP(A34,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I34" s="22">
+      <c r="I34">
         <f>E34-VLOOKUP(A34,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J34" s="22">
+      <c r="J34">
         <f>F34-VLOOKUP(A34,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -3650,15 +3649,15 @@
         <v>46143</v>
       </c>
       <c r="F35" s="5"/>
-      <c r="H35" s="22">
+      <c r="H35">
         <f>D35-VLOOKUP(A35,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I35" s="22">
+      <c r="I35">
         <f>E35-VLOOKUP(A35,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J35" s="22">
+      <c r="J35">
         <f>F35-VLOOKUP(A35,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -3676,22 +3675,22 @@
       <c r="D36" s="6">
         <v>46143</v>
       </c>
-      <c r="E36" s="26">
+      <c r="E36" s="25">
         <v>46165</v>
       </c>
       <c r="F36" s="5"/>
       <c r="G36" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="H36" s="22">
+      <c r="H36">
         <f>D36-VLOOKUP(A36,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I36" s="23">
+      <c r="I36" s="22">
         <f>E36-VLOOKUP(A36,'26035'!A:F,5,0)</f>
         <v>26</v>
       </c>
-      <c r="J36" s="22">
+      <c r="J36">
         <f>F36-VLOOKUP(A36,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -3709,19 +3708,19 @@
       <c r="D37" s="6">
         <v>46139</v>
       </c>
-      <c r="E37" s="26">
+      <c r="E37" s="25">
         <v>46165</v>
       </c>
       <c r="F37" s="5"/>
-      <c r="H37" s="22">
+      <c r="H37">
         <f>D37-VLOOKUP(A37,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I37" s="23">
+      <c r="I37" s="22">
         <f>E37-VLOOKUP(A37,'26035'!A:F,5,0)</f>
         <v>26</v>
       </c>
-      <c r="J37" s="22">
+      <c r="J37">
         <f>F37-VLOOKUP(A37,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -3739,19 +3738,19 @@
       <c r="D38" s="6">
         <v>46139</v>
       </c>
-      <c r="E38" s="26">
+      <c r="E38" s="25">
         <v>46165</v>
       </c>
       <c r="F38" s="5"/>
-      <c r="H38" s="22">
+      <c r="H38">
         <f>D38-VLOOKUP(A38,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I38" s="23">
+      <c r="I38" s="22">
         <f>E38-VLOOKUP(A38,'26035'!A:F,5,0)</f>
         <v>26</v>
       </c>
-      <c r="J38" s="22">
+      <c r="J38">
         <f>F38-VLOOKUP(A38,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -3769,19 +3768,19 @@
       <c r="D39" s="6">
         <v>46139</v>
       </c>
-      <c r="E39" s="26">
+      <c r="E39" s="25">
         <v>46165</v>
       </c>
       <c r="F39" s="5"/>
-      <c r="H39" s="22">
+      <c r="H39">
         <f>D39-VLOOKUP(A39,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I39" s="23">
+      <c r="I39" s="22">
         <f>E39-VLOOKUP(A39,'26035'!A:F,5,0)</f>
         <v>26</v>
       </c>
-      <c r="J39" s="22">
+      <c r="J39">
         <f>F39-VLOOKUP(A39,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -3799,19 +3798,19 @@
       <c r="D40" s="6">
         <v>46139</v>
       </c>
-      <c r="E40" s="26">
+      <c r="E40" s="25">
         <v>46165</v>
       </c>
       <c r="F40" s="5"/>
-      <c r="H40" s="22">
+      <c r="H40">
         <f>D40-VLOOKUP(A40,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I40" s="23">
+      <c r="I40" s="22">
         <f>E40-VLOOKUP(A40,'26035'!A:F,5,0)</f>
         <v>26</v>
       </c>
-      <c r="J40" s="22">
+      <c r="J40">
         <f>F40-VLOOKUP(A40,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -3829,19 +3828,19 @@
       <c r="D41" s="6">
         <v>46139</v>
       </c>
-      <c r="E41" s="26">
+      <c r="E41" s="25">
         <v>46165</v>
       </c>
       <c r="F41" s="5"/>
-      <c r="H41" s="22">
+      <c r="H41">
         <f>D41-VLOOKUP(A41,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I41" s="23">
+      <c r="I41" s="22">
         <f>E41-VLOOKUP(A41,'26035'!A:F,5,0)</f>
         <v>26</v>
       </c>
-      <c r="J41" s="22">
+      <c r="J41">
         <f>F41-VLOOKUP(A41,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -3859,19 +3858,19 @@
       <c r="D42" s="6">
         <v>46139</v>
       </c>
-      <c r="E42" s="26">
+      <c r="E42" s="25">
         <v>46165</v>
       </c>
       <c r="F42" s="5"/>
-      <c r="H42" s="22">
+      <c r="H42">
         <f>D42-VLOOKUP(A42,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I42" s="23">
+      <c r="I42" s="22">
         <f>E42-VLOOKUP(A42,'26035'!A:F,5,0)</f>
         <v>26</v>
       </c>
-      <c r="J42" s="22">
+      <c r="J42">
         <f>F42-VLOOKUP(A42,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -3889,22 +3888,22 @@
       <c r="D43" s="6">
         <v>46149</v>
       </c>
-      <c r="E43" s="26">
+      <c r="E43" s="25">
         <v>46173</v>
       </c>
       <c r="F43" s="5"/>
       <c r="G43" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="H43" s="22">
+      <c r="H43">
         <f>D43-VLOOKUP(A43,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I43" s="23">
+      <c r="I43" s="22">
         <f>E43-VLOOKUP(A43,'26035'!A:F,5,0)</f>
         <v>26</v>
       </c>
-      <c r="J43" s="22">
+      <c r="J43">
         <f>F43-VLOOKUP(A43,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -3922,19 +3921,19 @@
       <c r="D44" s="9">
         <v>46147</v>
       </c>
-      <c r="E44" s="26">
+      <c r="E44" s="25">
         <v>46173</v>
       </c>
       <c r="F44" s="8"/>
-      <c r="H44" s="22">
+      <c r="H44">
         <f>D44-VLOOKUP(A44,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I44" s="23">
+      <c r="I44" s="22">
         <f>E44-VLOOKUP(A44,'26035'!A:F,5,0)</f>
         <v>26</v>
       </c>
-      <c r="J44" s="22">
+      <c r="J44">
         <f>F44-VLOOKUP(A44,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -3952,19 +3951,19 @@
       <c r="D45" s="6">
         <v>46147</v>
       </c>
-      <c r="E45" s="26">
+      <c r="E45" s="25">
         <v>46173</v>
       </c>
       <c r="F45" s="5"/>
-      <c r="H45" s="22">
+      <c r="H45">
         <f>D45-VLOOKUP(A45,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I45" s="23">
+      <c r="I45" s="22">
         <f>E45-VLOOKUP(A45,'26035'!A:F,5,0)</f>
         <v>26</v>
       </c>
-      <c r="J45" s="22">
+      <c r="J45">
         <f>F45-VLOOKUP(A45,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -3982,19 +3981,19 @@
       <c r="D46" s="6">
         <v>46147</v>
       </c>
-      <c r="E46" s="26">
+      <c r="E46" s="25">
         <v>46173</v>
       </c>
       <c r="F46" s="5"/>
-      <c r="H46" s="22">
+      <c r="H46">
         <f>D46-VLOOKUP(A46,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I46" s="23">
+      <c r="I46" s="22">
         <f>E46-VLOOKUP(A46,'26035'!A:F,5,0)</f>
         <v>26</v>
       </c>
-      <c r="J46" s="22">
+      <c r="J46">
         <f>F46-VLOOKUP(A46,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -4012,19 +4011,19 @@
       <c r="D47" s="6">
         <v>46147</v>
       </c>
-      <c r="E47" s="26">
+      <c r="E47" s="25">
         <v>46173</v>
       </c>
       <c r="F47" s="5"/>
-      <c r="H47" s="22">
+      <c r="H47">
         <f>D47-VLOOKUP(A47,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I47" s="23">
+      <c r="I47" s="22">
         <f>E47-VLOOKUP(A47,'26035'!A:F,5,0)</f>
         <v>26</v>
       </c>
-      <c r="J47" s="22">
+      <c r="J47">
         <f>F47-VLOOKUP(A47,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -4042,19 +4041,19 @@
       <c r="D48" s="6">
         <v>46147</v>
       </c>
-      <c r="E48" s="26">
+      <c r="E48" s="25">
         <v>46173</v>
       </c>
       <c r="F48" s="5"/>
-      <c r="H48" s="22">
+      <c r="H48">
         <f>D48-VLOOKUP(A48,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I48" s="23">
+      <c r="I48" s="22">
         <f>E48-VLOOKUP(A48,'26035'!A:F,5,0)</f>
         <v>26</v>
       </c>
-      <c r="J48" s="22">
+      <c r="J48">
         <f>F48-VLOOKUP(A48,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -4072,19 +4071,19 @@
       <c r="D49" s="6">
         <v>46147</v>
       </c>
-      <c r="E49" s="26">
+      <c r="E49" s="25">
         <v>46173</v>
       </c>
       <c r="F49" s="5"/>
-      <c r="H49" s="22">
+      <c r="H49">
         <f>D49-VLOOKUP(A49,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I49" s="23">
+      <c r="I49" s="22">
         <f>E49-VLOOKUP(A49,'26035'!A:F,5,0)</f>
         <v>26</v>
       </c>
-      <c r="J49" s="22">
+      <c r="J49">
         <f>F49-VLOOKUP(A49,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -4102,19 +4101,19 @@
       <c r="D50" s="6">
         <v>46147</v>
       </c>
-      <c r="E50" s="26">
+      <c r="E50" s="25">
         <v>46173</v>
       </c>
       <c r="F50" s="5"/>
-      <c r="H50" s="22">
+      <c r="H50">
         <f>D50-VLOOKUP(A50,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I50" s="23">
+      <c r="I50" s="22">
         <f>E50-VLOOKUP(A50,'26035'!A:F,5,0)</f>
         <v>26</v>
       </c>
-      <c r="J50" s="22">
+      <c r="J50">
         <f>F50-VLOOKUP(A50,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -4136,15 +4135,15 @@
         <v>46156</v>
       </c>
       <c r="F51" s="5"/>
-      <c r="H51" s="22">
+      <c r="H51">
         <f>D51-VLOOKUP(A51,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I51" s="22">
+      <c r="I51">
         <f>E51-VLOOKUP(A51,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J51" s="22">
+      <c r="J51">
         <f>F51-VLOOKUP(A51,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -4168,15 +4167,15 @@
       <c r="F52" s="6">
         <v>46128</v>
       </c>
-      <c r="H52" s="22">
+      <c r="H52">
         <f>D52-VLOOKUP(A52,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I52" s="22">
+      <c r="I52">
         <f>E52-VLOOKUP(A52,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J52" s="22">
+      <c r="J52">
         <f>F52-VLOOKUP(A52,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -4198,15 +4197,15 @@
         <v>46154</v>
       </c>
       <c r="F53" s="5"/>
-      <c r="H53" s="22">
+      <c r="H53">
         <f>D53-VLOOKUP(A53,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I53" s="22">
+      <c r="I53">
         <f>E53-VLOOKUP(A53,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J53" s="22">
+      <c r="J53">
         <f>F53-VLOOKUP(A53,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -4224,22 +4223,22 @@
       <c r="D54" s="6">
         <v>46156</v>
       </c>
-      <c r="E54" s="26">
+      <c r="E54" s="25">
         <v>46182</v>
       </c>
       <c r="F54" s="5"/>
       <c r="G54" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="H54" s="22">
+      <c r="H54">
         <f>D54-VLOOKUP(A54,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I54" s="23">
+      <c r="I54" s="22">
         <f>E54-VLOOKUP(A54,'26035'!A:F,5,0)</f>
         <v>26</v>
       </c>
-      <c r="J54" s="22">
+      <c r="J54">
         <f>F54-VLOOKUP(A54,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -4257,22 +4256,22 @@
       <c r="D55" s="6">
         <v>46165</v>
       </c>
-      <c r="E55" s="26">
+      <c r="E55" s="25">
         <v>46191</v>
       </c>
       <c r="F55" s="5"/>
       <c r="G55" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="H55" s="22">
+      <c r="H55">
         <f>D55-VLOOKUP(A55,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I55" s="23">
+      <c r="I55" s="22">
         <f>E55-VLOOKUP(A55,'26035'!A:F,5,0)</f>
         <v>26</v>
       </c>
-      <c r="J55" s="22">
+      <c r="J55">
         <f>F55-VLOOKUP(A55,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -4290,22 +4289,22 @@
       <c r="D56" s="6">
         <v>46167</v>
       </c>
-      <c r="E56" s="26">
+      <c r="E56" s="25">
         <v>46193</v>
       </c>
       <c r="F56" s="5"/>
       <c r="G56" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="H56" s="22">
+      <c r="H56">
         <f>D56-VLOOKUP(A56,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I56" s="23">
+      <c r="I56" s="22">
         <f>E56-VLOOKUP(A56,'26035'!A:F,5,0)</f>
         <v>26</v>
       </c>
-      <c r="J56" s="22">
+      <c r="J56">
         <f>F56-VLOOKUP(A56,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -4327,15 +4326,15 @@
         <v>46171</v>
       </c>
       <c r="F57" s="5"/>
-      <c r="H57" s="22">
+      <c r="H57">
         <f>D57-VLOOKUP(A57,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I57" s="22">
+      <c r="I57">
         <f>E57-VLOOKUP(A57,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J57" s="22">
+      <c r="J57">
         <f>F57-VLOOKUP(A57,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -4357,15 +4356,15 @@
         <v>46096</v>
       </c>
       <c r="F58" s="11"/>
-      <c r="H58" s="22">
+      <c r="H58">
         <f>D58-VLOOKUP(A58,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I58" s="22">
+      <c r="I58">
         <f>E58-VLOOKUP(A58,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J58" s="22">
+      <c r="J58">
         <f>F58-VLOOKUP(A58,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -4377,7 +4376,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{091CD8ED-919E-4201-9620-E3042FC90D2E}">
-  <sheetPr>
+  <sheetPr codeName="Sheet3">
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
   <dimension ref="A1:J58"/>
@@ -4390,8 +4389,8 @@
     <col min="5" max="5" width="21.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="17.42578125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.42578125" style="13" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.5703125" style="22" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="11.85546875" style="22" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="11.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4416,13 +4415,13 @@
       <c r="G1" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="H1" s="22" t="s">
+      <c r="H1" t="s">
         <v>110</v>
       </c>
-      <c r="I1" s="22" t="s">
+      <c r="I1" t="s">
         <v>111</v>
       </c>
-      <c r="J1" s="22" t="s">
+      <c r="J1" t="s">
         <v>112</v>
       </c>
     </row>
@@ -4443,15 +4442,15 @@
         <v>46089</v>
       </c>
       <c r="F2" s="2"/>
-      <c r="H2" s="22">
+      <c r="H2">
         <f>D2-VLOOKUP(A2,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I2" s="22">
+      <c r="I2">
         <f>E2-VLOOKUP(A2,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J2" s="22">
+      <c r="J2">
         <f>F2-VLOOKUP(A2,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -4473,15 +4472,15 @@
         <v>46094</v>
       </c>
       <c r="F3" s="5"/>
-      <c r="H3" s="22">
+      <c r="H3">
         <f>D3-VLOOKUP(A3,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I3" s="22">
+      <c r="I3">
         <f>E3-VLOOKUP(A3,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J3" s="22">
+      <c r="J3">
         <f>F3-VLOOKUP(A3,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -4508,15 +4507,15 @@
       <c r="G4" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="H4" s="22">
+      <c r="H4">
         <f>D4-VLOOKUP(A4,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I4" s="22">
+      <c r="I4">
         <f>E4-VLOOKUP(A4,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J4" s="22">
+      <c r="J4">
         <f>F4-VLOOKUP(A4,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -4538,15 +4537,15 @@
         <v>46103</v>
       </c>
       <c r="F5" s="5"/>
-      <c r="H5" s="22">
+      <c r="H5">
         <f>D5-VLOOKUP(A5,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I5" s="22">
+      <c r="I5">
         <f>E5-VLOOKUP(A5,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J5" s="22">
+      <c r="J5">
         <f>F5-VLOOKUP(A5,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -4568,15 +4567,15 @@
         <v>46107</v>
       </c>
       <c r="F6" s="5"/>
-      <c r="H6" s="22">
+      <c r="H6">
         <f>D6-VLOOKUP(A6,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I6" s="22">
+      <c r="I6">
         <f>E6-VLOOKUP(A6,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J6" s="22">
+      <c r="J6">
         <f>F6-VLOOKUP(A6,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -4598,15 +4597,15 @@
         <v>46114</v>
       </c>
       <c r="F7" s="5"/>
-      <c r="H7" s="22">
+      <c r="H7">
         <f>D7-VLOOKUP(A7,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I7" s="22">
+      <c r="I7">
         <f>E7-VLOOKUP(A7,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J7" s="22">
+      <c r="J7">
         <f>F7-VLOOKUP(A7,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -4628,15 +4627,15 @@
         <v>46109</v>
       </c>
       <c r="F8" s="5"/>
-      <c r="H8" s="22">
+      <c r="H8">
         <f>D8-VLOOKUP(A8,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I8" s="22">
+      <c r="I8">
         <f>E8-VLOOKUP(A8,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J8" s="22">
+      <c r="J8">
         <f>F8-VLOOKUP(A8,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -4658,15 +4657,15 @@
         <v>46109</v>
       </c>
       <c r="F9" s="5"/>
-      <c r="H9" s="22">
+      <c r="H9">
         <f>D9-VLOOKUP(A9,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I9" s="22">
+      <c r="I9">
         <f>E9-VLOOKUP(A9,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J9" s="22">
+      <c r="J9">
         <f>F9-VLOOKUP(A9,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -4688,15 +4687,15 @@
         <v>46109</v>
       </c>
       <c r="F10" s="5"/>
-      <c r="H10" s="22">
+      <c r="H10">
         <f>D10-VLOOKUP(A10,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I10" s="22">
+      <c r="I10">
         <f>E10-VLOOKUP(A10,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J10" s="22">
+      <c r="J10">
         <f>F10-VLOOKUP(A10,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -4718,15 +4717,15 @@
         <v>46109</v>
       </c>
       <c r="F11" s="5"/>
-      <c r="H11" s="22">
+      <c r="H11">
         <f>D11-VLOOKUP(A11,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I11" s="22">
+      <c r="I11">
         <f>E11-VLOOKUP(A11,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J11" s="22">
+      <c r="J11">
         <f>F11-VLOOKUP(A11,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -4748,15 +4747,15 @@
         <v>46109</v>
       </c>
       <c r="F12" s="5"/>
-      <c r="H12" s="22">
+      <c r="H12">
         <f>D12-VLOOKUP(A12,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I12" s="22">
+      <c r="I12">
         <f>E12-VLOOKUP(A12,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J12" s="22">
+      <c r="J12">
         <f>F12-VLOOKUP(A12,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -4778,15 +4777,15 @@
         <v>46109</v>
       </c>
       <c r="F13" s="5"/>
-      <c r="H13" s="22">
+      <c r="H13">
         <f>D13-VLOOKUP(A13,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I13" s="22">
+      <c r="I13">
         <f>E13-VLOOKUP(A13,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J13" s="22">
+      <c r="J13">
         <f>F13-VLOOKUP(A13,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -4808,15 +4807,15 @@
         <v>46109</v>
       </c>
       <c r="F14" s="5"/>
-      <c r="H14" s="22">
+      <c r="H14">
         <f>D14-VLOOKUP(A14,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I14" s="22">
+      <c r="I14">
         <f>E14-VLOOKUP(A14,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J14" s="22">
+      <c r="J14">
         <f>F14-VLOOKUP(A14,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -4838,15 +4837,15 @@
         <v>46109</v>
       </c>
       <c r="F15" s="5"/>
-      <c r="H15" s="22">
+      <c r="H15">
         <f>D15-VLOOKUP(A15,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I15" s="22">
+      <c r="I15">
         <f>E15-VLOOKUP(A15,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J15" s="22">
+      <c r="J15">
         <f>F15-VLOOKUP(A15,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -4868,15 +4867,15 @@
         <v>46108</v>
       </c>
       <c r="F16" s="5"/>
-      <c r="H16" s="22">
+      <c r="H16">
         <f>D16-VLOOKUP(A16,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I16" s="22">
+      <c r="I16">
         <f>E16-VLOOKUP(A16,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J16" s="22">
+      <c r="J16">
         <f>F16-VLOOKUP(A16,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -4898,15 +4897,15 @@
         <v>46109</v>
       </c>
       <c r="F17" s="5"/>
-      <c r="H17" s="22">
+      <c r="H17">
         <f>D17-VLOOKUP(A17,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I17" s="22">
+      <c r="I17">
         <f>E17-VLOOKUP(A17,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J17" s="22">
+      <c r="J17">
         <f>F17-VLOOKUP(A17,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -4928,15 +4927,15 @@
         <v>46115</v>
       </c>
       <c r="F18" s="5"/>
-      <c r="H18" s="22">
+      <c r="H18">
         <f>D18-VLOOKUP(A18,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I18" s="22">
+      <c r="I18">
         <f>E18-VLOOKUP(A18,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J18" s="22">
+      <c r="J18">
         <f>F18-VLOOKUP(A18,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -4961,15 +4960,15 @@
       <c r="G19" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="H19" s="22">
+      <c r="H19">
         <f>D19-VLOOKUP(A19,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I19" s="22">
+      <c r="I19">
         <f>E19-VLOOKUP(A19,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J19" s="22">
+      <c r="J19">
         <f>F19-VLOOKUP(A19,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -4991,15 +4990,15 @@
         <v>46108</v>
       </c>
       <c r="F20" s="5"/>
-      <c r="H20" s="22">
+      <c r="H20">
         <f>D20-VLOOKUP(A20,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I20" s="22">
+      <c r="I20">
         <f>E20-VLOOKUP(A20,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J20" s="22">
+      <c r="J20">
         <f>F20-VLOOKUP(A20,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -5021,15 +5020,15 @@
         <v>46108</v>
       </c>
       <c r="F21" s="5"/>
-      <c r="H21" s="22">
+      <c r="H21">
         <f>D21-VLOOKUP(A21,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I21" s="22">
+      <c r="I21">
         <f>E21-VLOOKUP(A21,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J21" s="22">
+      <c r="J21">
         <f>F21-VLOOKUP(A21,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -5051,15 +5050,15 @@
         <v>46108</v>
       </c>
       <c r="F22" s="5"/>
-      <c r="H22" s="22">
+      <c r="H22">
         <f>D22-VLOOKUP(A22,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I22" s="22">
+      <c r="I22">
         <f>E22-VLOOKUP(A22,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J22" s="22">
+      <c r="J22">
         <f>F22-VLOOKUP(A22,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -5081,15 +5080,15 @@
         <v>46108</v>
       </c>
       <c r="F23" s="5"/>
-      <c r="H23" s="22">
+      <c r="H23">
         <f>D23-VLOOKUP(A23,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I23" s="22">
+      <c r="I23">
         <f>E23-VLOOKUP(A23,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J23" s="22">
+      <c r="J23">
         <f>F23-VLOOKUP(A23,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -5111,15 +5110,15 @@
         <v>46108</v>
       </c>
       <c r="F24" s="5"/>
-      <c r="H24" s="22">
+      <c r="H24">
         <f>D24-VLOOKUP(A24,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I24" s="22">
+      <c r="I24">
         <f>E24-VLOOKUP(A24,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J24" s="22">
+      <c r="J24">
         <f>F24-VLOOKUP(A24,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -5141,15 +5140,15 @@
         <v>46108</v>
       </c>
       <c r="F25" s="5"/>
-      <c r="H25" s="22">
+      <c r="H25">
         <f>D25-VLOOKUP(A25,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I25" s="22">
+      <c r="I25">
         <f>E25-VLOOKUP(A25,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J25" s="22">
+      <c r="J25">
         <f>F25-VLOOKUP(A25,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -5171,15 +5170,15 @@
         <v>46104</v>
       </c>
       <c r="F26" s="5"/>
-      <c r="H26" s="22">
+      <c r="H26">
         <f>D26-VLOOKUP(A26,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I26" s="22">
+      <c r="I26">
         <f>E26-VLOOKUP(A26,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J26" s="22">
+      <c r="J26">
         <f>F26-VLOOKUP(A26,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -5201,15 +5200,15 @@
         <v>46113</v>
       </c>
       <c r="F27" s="5"/>
-      <c r="H27" s="22">
+      <c r="H27">
         <f>D27-VLOOKUP(A27,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I27" s="22">
+      <c r="I27">
         <f>E27-VLOOKUP(A27,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J27" s="22">
+      <c r="J27">
         <f>F27-VLOOKUP(A27,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -5231,15 +5230,15 @@
         <v>46114</v>
       </c>
       <c r="F28" s="5"/>
-      <c r="H28" s="22">
+      <c r="H28">
         <f>D28-VLOOKUP(A28,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I28" s="22">
+      <c r="I28">
         <f>E28-VLOOKUP(A28,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J28" s="22">
+      <c r="J28">
         <f>F28-VLOOKUP(A28,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -5261,15 +5260,15 @@
         <v>46118</v>
       </c>
       <c r="F29" s="5"/>
-      <c r="H29" s="22">
+      <c r="H29">
         <f>D29-VLOOKUP(A29,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I29" s="22">
+      <c r="I29">
         <f>E29-VLOOKUP(A29,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J29" s="22">
+      <c r="J29">
         <f>F29-VLOOKUP(A29,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -5291,15 +5290,15 @@
         <v>46124</v>
       </c>
       <c r="F30" s="5"/>
-      <c r="H30" s="22">
+      <c r="H30">
         <f>D30-VLOOKUP(A30,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I30" s="22">
+      <c r="I30">
         <f>E30-VLOOKUP(A30,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J30" s="22">
+      <c r="J30">
         <f>F30-VLOOKUP(A30,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -5321,15 +5320,15 @@
         <v>46137</v>
       </c>
       <c r="F31" s="5"/>
-      <c r="H31" s="22">
+      <c r="H31">
         <f>D31-VLOOKUP(A31,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I31" s="22">
+      <c r="I31">
         <f>E31-VLOOKUP(A31,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J31" s="22">
+      <c r="J31">
         <f>F31-VLOOKUP(A31,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -5354,15 +5353,15 @@
       <c r="G32" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="H32" s="22">
+      <c r="H32">
         <f>D32-VLOOKUP(A32,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I32" s="22">
+      <c r="I32">
         <f>E32-VLOOKUP(A32,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J32" s="22">
+      <c r="J32">
         <f>F32-VLOOKUP(A32,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -5387,15 +5386,15 @@
       <c r="G33" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="H33" s="22">
+      <c r="H33">
         <f>D33-VLOOKUP(A33,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I33" s="22">
+      <c r="I33">
         <f>E33-VLOOKUP(A33,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J33" s="22">
+      <c r="J33">
         <f>F33-VLOOKUP(A33,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -5420,15 +5419,15 @@
       <c r="G34" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="H34" s="22">
+      <c r="H34">
         <f>D34-VLOOKUP(A34,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I34" s="22">
+      <c r="I34">
         <f>E34-VLOOKUP(A34,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J34" s="22">
+      <c r="J34">
         <f>F34-VLOOKUP(A34,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -5450,15 +5449,15 @@
         <v>46143</v>
       </c>
       <c r="F35" s="5"/>
-      <c r="H35" s="22">
+      <c r="H35">
         <f>D35-VLOOKUP(A35,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I35" s="22">
+      <c r="I35">
         <f>E35-VLOOKUP(A35,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J35" s="22">
+      <c r="J35">
         <f>F35-VLOOKUP(A35,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -5483,15 +5482,15 @@
       <c r="G36" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="H36" s="22">
+      <c r="H36">
         <f>D36-VLOOKUP(A36,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I36" s="22">
+      <c r="I36">
         <f>E36-VLOOKUP(A36,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J36" s="22">
+      <c r="J36">
         <f>F36-VLOOKUP(A36,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -5513,15 +5512,15 @@
         <v>46139</v>
       </c>
       <c r="F37" s="5"/>
-      <c r="H37" s="22">
+      <c r="H37">
         <f>D37-VLOOKUP(A37,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I37" s="22">
+      <c r="I37">
         <f>E37-VLOOKUP(A37,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J37" s="22">
+      <c r="J37">
         <f>F37-VLOOKUP(A37,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -5543,15 +5542,15 @@
         <v>46139</v>
       </c>
       <c r="F38" s="5"/>
-      <c r="H38" s="22">
+      <c r="H38">
         <f>D38-VLOOKUP(A38,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I38" s="22">
+      <c r="I38">
         <f>E38-VLOOKUP(A38,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J38" s="22">
+      <c r="J38">
         <f>F38-VLOOKUP(A38,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -5573,15 +5572,15 @@
         <v>46139</v>
       </c>
       <c r="F39" s="5"/>
-      <c r="H39" s="22">
+      <c r="H39">
         <f>D39-VLOOKUP(A39,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I39" s="22">
+      <c r="I39">
         <f>E39-VLOOKUP(A39,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J39" s="22">
+      <c r="J39">
         <f>F39-VLOOKUP(A39,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -5603,15 +5602,15 @@
         <v>46139</v>
       </c>
       <c r="F40" s="5"/>
-      <c r="H40" s="22">
+      <c r="H40">
         <f>D40-VLOOKUP(A40,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I40" s="22">
+      <c r="I40">
         <f>E40-VLOOKUP(A40,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J40" s="22">
+      <c r="J40">
         <f>F40-VLOOKUP(A40,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -5633,15 +5632,15 @@
         <v>46139</v>
       </c>
       <c r="F41" s="5"/>
-      <c r="H41" s="22">
+      <c r="H41">
         <f>D41-VLOOKUP(A41,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I41" s="22">
+      <c r="I41">
         <f>E41-VLOOKUP(A41,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J41" s="22">
+      <c r="J41">
         <f>F41-VLOOKUP(A41,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -5663,15 +5662,15 @@
         <v>46139</v>
       </c>
       <c r="F42" s="5"/>
-      <c r="H42" s="22">
+      <c r="H42">
         <f>D42-VLOOKUP(A42,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I42" s="22">
+      <c r="I42">
         <f>E42-VLOOKUP(A42,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J42" s="22">
+      <c r="J42">
         <f>F42-VLOOKUP(A42,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -5696,15 +5695,15 @@
       <c r="G43" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="H43" s="22">
+      <c r="H43">
         <f>D43-VLOOKUP(A43,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I43" s="22">
+      <c r="I43">
         <f>E43-VLOOKUP(A43,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J43" s="22">
+      <c r="J43">
         <f>F43-VLOOKUP(A43,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -5726,15 +5725,15 @@
         <v>46147</v>
       </c>
       <c r="F44" s="8"/>
-      <c r="H44" s="22">
+      <c r="H44">
         <f>D44-VLOOKUP(A44,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I44" s="22">
+      <c r="I44">
         <f>E44-VLOOKUP(A44,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J44" s="22">
+      <c r="J44">
         <f>F44-VLOOKUP(A44,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -5756,15 +5755,15 @@
         <v>46147</v>
       </c>
       <c r="F45" s="5"/>
-      <c r="H45" s="22">
+      <c r="H45">
         <f>D45-VLOOKUP(A45,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I45" s="22">
+      <c r="I45">
         <f>E45-VLOOKUP(A45,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J45" s="22">
+      <c r="J45">
         <f>F45-VLOOKUP(A45,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -5786,15 +5785,15 @@
         <v>46147</v>
       </c>
       <c r="F46" s="5"/>
-      <c r="H46" s="22">
+      <c r="H46">
         <f>D46-VLOOKUP(A46,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I46" s="22">
+      <c r="I46">
         <f>E46-VLOOKUP(A46,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J46" s="22">
+      <c r="J46">
         <f>F46-VLOOKUP(A46,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -5816,15 +5815,15 @@
         <v>46147</v>
       </c>
       <c r="F47" s="5"/>
-      <c r="H47" s="22">
+      <c r="H47">
         <f>D47-VLOOKUP(A47,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I47" s="22">
+      <c r="I47">
         <f>E47-VLOOKUP(A47,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J47" s="22">
+      <c r="J47">
         <f>F47-VLOOKUP(A47,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -5846,15 +5845,15 @@
         <v>46147</v>
       </c>
       <c r="F48" s="5"/>
-      <c r="H48" s="22">
+      <c r="H48">
         <f>D48-VLOOKUP(A48,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I48" s="22">
+      <c r="I48">
         <f>E48-VLOOKUP(A48,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J48" s="22">
+      <c r="J48">
         <f>F48-VLOOKUP(A48,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -5876,15 +5875,15 @@
         <v>46147</v>
       </c>
       <c r="F49" s="5"/>
-      <c r="H49" s="22">
+      <c r="H49">
         <f>D49-VLOOKUP(A49,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I49" s="22">
+      <c r="I49">
         <f>E49-VLOOKUP(A49,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J49" s="22">
+      <c r="J49">
         <f>F49-VLOOKUP(A49,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -5906,15 +5905,15 @@
         <v>46147</v>
       </c>
       <c r="F50" s="5"/>
-      <c r="H50" s="22">
+      <c r="H50">
         <f>D50-VLOOKUP(A50,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I50" s="22">
+      <c r="I50">
         <f>E50-VLOOKUP(A50,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J50" s="22">
+      <c r="J50">
         <f>F50-VLOOKUP(A50,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -5936,15 +5935,15 @@
         <v>46156</v>
       </c>
       <c r="F51" s="5"/>
-      <c r="H51" s="22">
+      <c r="H51">
         <f>D51-VLOOKUP(A51,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I51" s="22">
+      <c r="I51">
         <f>E51-VLOOKUP(A51,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J51" s="22">
+      <c r="J51">
         <f>F51-VLOOKUP(A51,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -5968,15 +5967,15 @@
       <c r="F52" s="6">
         <v>46128</v>
       </c>
-      <c r="H52" s="22">
+      <c r="H52">
         <f>D52-VLOOKUP(A52,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I52" s="22">
+      <c r="I52">
         <f>E52-VLOOKUP(A52,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J52" s="22">
+      <c r="J52">
         <f>F52-VLOOKUP(A52,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -5998,15 +5997,15 @@
         <v>46154</v>
       </c>
       <c r="F53" s="5"/>
-      <c r="H53" s="22">
+      <c r="H53">
         <f>D53-VLOOKUP(A53,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I53" s="22">
+      <c r="I53">
         <f>E53-VLOOKUP(A53,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J53" s="22">
+      <c r="J53">
         <f>F53-VLOOKUP(A53,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -6031,15 +6030,15 @@
       <c r="G54" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="H54" s="22">
+      <c r="H54">
         <f>D54-VLOOKUP(A54,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I54" s="22">
+      <c r="I54">
         <f>E54-VLOOKUP(A54,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J54" s="22">
+      <c r="J54">
         <f>F54-VLOOKUP(A54,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -6064,15 +6063,15 @@
       <c r="G55" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="H55" s="22">
+      <c r="H55">
         <f>D55-VLOOKUP(A55,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I55" s="22">
+      <c r="I55">
         <f>E55-VLOOKUP(A55,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J55" s="22">
+      <c r="J55">
         <f>F55-VLOOKUP(A55,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -6097,15 +6096,15 @@
       <c r="G56" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="H56" s="22">
+      <c r="H56">
         <f>D56-VLOOKUP(A56,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I56" s="22">
+      <c r="I56">
         <f>E56-VLOOKUP(A56,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J56" s="22">
+      <c r="J56">
         <f>F56-VLOOKUP(A56,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -6127,15 +6126,15 @@
         <v>46171</v>
       </c>
       <c r="F57" s="5"/>
-      <c r="H57" s="22">
+      <c r="H57">
         <f>D57-VLOOKUP(A57,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I57" s="22">
+      <c r="I57">
         <f>E57-VLOOKUP(A57,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J57" s="22">
+      <c r="J57">
         <f>F57-VLOOKUP(A57,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -6157,15 +6156,15 @@
         <v>46096</v>
       </c>
       <c r="F58" s="11"/>
-      <c r="H58" s="22">
+      <c r="H58">
         <f>D58-VLOOKUP(A58,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I58" s="22">
+      <c r="I58">
         <f>E58-VLOOKUP(A58,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J58" s="22">
+      <c r="J58">
         <f>F58-VLOOKUP(A58,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -6178,6 +6177,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0DF8CA0-8B44-45C0-8FFE-F40C3281B0C9}">
+  <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:K58"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -6188,8 +6188,8 @@
     <col min="5" max="5" width="21.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="17.42578125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.42578125" style="13" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.5703125" style="22" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="11.85546875" style="22" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="11.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -6214,13 +6214,13 @@
       <c r="G1" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="H1" s="22" t="s">
+      <c r="H1" t="s">
         <v>110</v>
       </c>
-      <c r="I1" s="22" t="s">
+      <c r="I1" t="s">
         <v>111</v>
       </c>
-      <c r="J1" s="22" t="s">
+      <c r="J1" t="s">
         <v>112</v>
       </c>
     </row>
@@ -6241,15 +6241,15 @@
         <v>46089</v>
       </c>
       <c r="F2" s="2"/>
-      <c r="H2" s="22">
+      <c r="H2">
         <f>D2-VLOOKUP(A2,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I2" s="22">
+      <c r="I2">
         <f>E2-VLOOKUP(A2,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J2" s="22">
+      <c r="J2">
         <f>F2-VLOOKUP(A2,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -6271,15 +6271,15 @@
         <v>46094</v>
       </c>
       <c r="F3" s="5"/>
-      <c r="H3" s="22">
+      <c r="H3">
         <f>D3-VLOOKUP(A3,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I3" s="22">
+      <c r="I3">
         <f>E3-VLOOKUP(A3,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J3" s="22">
+      <c r="J3">
         <f>F3-VLOOKUP(A3,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -6306,15 +6306,15 @@
       <c r="G4" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="H4" s="22">
+      <c r="H4">
         <f>D4-VLOOKUP(A4,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I4" s="22">
+      <c r="I4">
         <f>E4-VLOOKUP(A4,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J4" s="22">
+      <c r="J4">
         <f>F4-VLOOKUP(A4,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -6336,15 +6336,15 @@
         <v>46103</v>
       </c>
       <c r="F5" s="5"/>
-      <c r="H5" s="22">
+      <c r="H5">
         <f>D5-VLOOKUP(A5,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I5" s="22">
+      <c r="I5">
         <f>E5-VLOOKUP(A5,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J5" s="22">
+      <c r="J5">
         <f>F5-VLOOKUP(A5,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -6366,15 +6366,15 @@
         <v>46107</v>
       </c>
       <c r="F6" s="5"/>
-      <c r="H6" s="22">
+      <c r="H6">
         <f>D6-VLOOKUP(A6,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I6" s="22">
+      <c r="I6">
         <f>E6-VLOOKUP(A6,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J6" s="22">
+      <c r="J6">
         <f>F6-VLOOKUP(A6,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -6396,15 +6396,15 @@
         <v>46114</v>
       </c>
       <c r="F7" s="5"/>
-      <c r="H7" s="22">
+      <c r="H7">
         <f>D7-VLOOKUP(A7,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I7" s="22">
+      <c r="I7">
         <f>E7-VLOOKUP(A7,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J7" s="22">
+      <c r="J7">
         <f>F7-VLOOKUP(A7,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -6426,15 +6426,15 @@
         <v>46109</v>
       </c>
       <c r="F8" s="5"/>
-      <c r="H8" s="22">
+      <c r="H8">
         <f>D8-VLOOKUP(A8,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I8" s="22">
+      <c r="I8">
         <f>E8-VLOOKUP(A8,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J8" s="22">
+      <c r="J8">
         <f>F8-VLOOKUP(A8,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -6456,15 +6456,15 @@
         <v>46109</v>
       </c>
       <c r="F9" s="5"/>
-      <c r="H9" s="22">
+      <c r="H9">
         <f>D9-VLOOKUP(A9,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I9" s="22">
+      <c r="I9">
         <f>E9-VLOOKUP(A9,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J9" s="22">
+      <c r="J9">
         <f>F9-VLOOKUP(A9,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -6486,15 +6486,15 @@
         <v>46109</v>
       </c>
       <c r="F10" s="5"/>
-      <c r="H10" s="22">
+      <c r="H10">
         <f>D10-VLOOKUP(A10,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I10" s="22">
+      <c r="I10">
         <f>E10-VLOOKUP(A10,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J10" s="22">
+      <c r="J10">
         <f>F10-VLOOKUP(A10,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -6516,15 +6516,15 @@
         <v>46109</v>
       </c>
       <c r="F11" s="5"/>
-      <c r="H11" s="22">
+      <c r="H11">
         <f>D11-VLOOKUP(A11,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I11" s="22">
+      <c r="I11">
         <f>E11-VLOOKUP(A11,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J11" s="22">
+      <c r="J11">
         <f>F11-VLOOKUP(A11,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -6546,15 +6546,15 @@
         <v>46109</v>
       </c>
       <c r="F12" s="5"/>
-      <c r="H12" s="22">
+      <c r="H12">
         <f>D12-VLOOKUP(A12,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I12" s="22">
+      <c r="I12">
         <f>E12-VLOOKUP(A12,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J12" s="22">
+      <c r="J12">
         <f>F12-VLOOKUP(A12,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -6576,15 +6576,15 @@
         <v>46109</v>
       </c>
       <c r="F13" s="5"/>
-      <c r="H13" s="22">
+      <c r="H13">
         <f>D13-VLOOKUP(A13,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I13" s="22">
+      <c r="I13">
         <f>E13-VLOOKUP(A13,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J13" s="22">
+      <c r="J13">
         <f>F13-VLOOKUP(A13,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -6606,15 +6606,15 @@
         <v>46109</v>
       </c>
       <c r="F14" s="5"/>
-      <c r="H14" s="22">
+      <c r="H14">
         <f>D14-VLOOKUP(A14,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I14" s="22">
+      <c r="I14">
         <f>E14-VLOOKUP(A14,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J14" s="22">
+      <c r="J14">
         <f>F14-VLOOKUP(A14,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -6636,15 +6636,15 @@
         <v>46109</v>
       </c>
       <c r="F15" s="5"/>
-      <c r="H15" s="22">
+      <c r="H15">
         <f>D15-VLOOKUP(A15,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I15" s="22">
+      <c r="I15">
         <f>E15-VLOOKUP(A15,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J15" s="22">
+      <c r="J15">
         <f>F15-VLOOKUP(A15,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -6666,15 +6666,15 @@
         <v>46108</v>
       </c>
       <c r="F16" s="5"/>
-      <c r="H16" s="22">
+      <c r="H16">
         <f>D16-VLOOKUP(A16,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I16" s="22">
+      <c r="I16">
         <f>E16-VLOOKUP(A16,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J16" s="22">
+      <c r="J16">
         <f>F16-VLOOKUP(A16,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -6696,15 +6696,15 @@
         <v>46109</v>
       </c>
       <c r="F17" s="5"/>
-      <c r="H17" s="22">
+      <c r="H17">
         <f>D17-VLOOKUP(A17,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I17" s="22">
+      <c r="I17">
         <f>E17-VLOOKUP(A17,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J17" s="22">
+      <c r="J17">
         <f>F17-VLOOKUP(A17,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -6726,15 +6726,15 @@
         <v>46115</v>
       </c>
       <c r="F18" s="5"/>
-      <c r="H18" s="22">
+      <c r="H18">
         <f>D18-VLOOKUP(A18,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I18" s="22">
+      <c r="I18">
         <f>E18-VLOOKUP(A18,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J18" s="22">
+      <c r="J18">
         <f>F18-VLOOKUP(A18,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -6759,15 +6759,15 @@
       <c r="G19" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="H19" s="22">
+      <c r="H19">
         <f>D19-VLOOKUP(A19,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I19" s="22">
+      <c r="I19">
         <f>E19-VLOOKUP(A19,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J19" s="22">
+      <c r="J19">
         <f>F19-VLOOKUP(A19,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -6789,15 +6789,15 @@
         <v>46108</v>
       </c>
       <c r="F20" s="5"/>
-      <c r="H20" s="22">
+      <c r="H20">
         <f>D20-VLOOKUP(A20,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I20" s="22">
+      <c r="I20">
         <f>E20-VLOOKUP(A20,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J20" s="22">
+      <c r="J20">
         <f>F20-VLOOKUP(A20,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -6819,15 +6819,15 @@
         <v>46108</v>
       </c>
       <c r="F21" s="5"/>
-      <c r="H21" s="22">
+      <c r="H21">
         <f>D21-VLOOKUP(A21,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I21" s="22">
+      <c r="I21">
         <f>E21-VLOOKUP(A21,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J21" s="22">
+      <c r="J21">
         <f>F21-VLOOKUP(A21,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -6849,15 +6849,15 @@
         <v>46108</v>
       </c>
       <c r="F22" s="5"/>
-      <c r="H22" s="22">
+      <c r="H22">
         <f>D22-VLOOKUP(A22,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I22" s="22">
+      <c r="I22">
         <f>E22-VLOOKUP(A22,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J22" s="22">
+      <c r="J22">
         <f>F22-VLOOKUP(A22,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -6879,15 +6879,15 @@
         <v>46108</v>
       </c>
       <c r="F23" s="5"/>
-      <c r="H23" s="22">
+      <c r="H23">
         <f>D23-VLOOKUP(A23,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I23" s="22">
+      <c r="I23">
         <f>E23-VLOOKUP(A23,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J23" s="22">
+      <c r="J23">
         <f>F23-VLOOKUP(A23,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -6909,15 +6909,15 @@
         <v>46108</v>
       </c>
       <c r="F24" s="5"/>
-      <c r="H24" s="22">
+      <c r="H24">
         <f>D24-VLOOKUP(A24,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I24" s="22">
+      <c r="I24">
         <f>E24-VLOOKUP(A24,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J24" s="22">
+      <c r="J24">
         <f>F24-VLOOKUP(A24,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -6939,15 +6939,15 @@
         <v>46108</v>
       </c>
       <c r="F25" s="5"/>
-      <c r="H25" s="22">
+      <c r="H25">
         <f>D25-VLOOKUP(A25,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I25" s="22">
+      <c r="I25">
         <f>E25-VLOOKUP(A25,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J25" s="22">
+      <c r="J25">
         <f>F25-VLOOKUP(A25,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -6969,15 +6969,15 @@
         <v>46104</v>
       </c>
       <c r="F26" s="5"/>
-      <c r="H26" s="22">
+      <c r="H26">
         <f>D26-VLOOKUP(A26,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I26" s="22">
+      <c r="I26">
         <f>E26-VLOOKUP(A26,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J26" s="22">
+      <c r="J26">
         <f>F26-VLOOKUP(A26,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -6999,15 +6999,15 @@
         <v>46113</v>
       </c>
       <c r="F27" s="5"/>
-      <c r="H27" s="22">
+      <c r="H27">
         <f>D27-VLOOKUP(A27,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I27" s="22">
+      <c r="I27">
         <f>E27-VLOOKUP(A27,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J27" s="22">
+      <c r="J27">
         <f>F27-VLOOKUP(A27,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -7029,15 +7029,15 @@
         <v>46114</v>
       </c>
       <c r="F28" s="5"/>
-      <c r="H28" s="22">
+      <c r="H28">
         <f>D28-VLOOKUP(A28,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I28" s="22">
+      <c r="I28">
         <f>E28-VLOOKUP(A28,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J28" s="22">
+      <c r="J28">
         <f>F28-VLOOKUP(A28,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -7059,15 +7059,15 @@
         <v>46118</v>
       </c>
       <c r="F29" s="5"/>
-      <c r="H29" s="22">
+      <c r="H29">
         <f>D29-VLOOKUP(A29,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I29" s="22">
+      <c r="I29">
         <f>E29-VLOOKUP(A29,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J29" s="22">
+      <c r="J29">
         <f>F29-VLOOKUP(A29,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -7089,15 +7089,15 @@
         <v>46124</v>
       </c>
       <c r="F30" s="5"/>
-      <c r="H30" s="22">
+      <c r="H30">
         <f>D30-VLOOKUP(A30,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I30" s="22">
+      <c r="I30">
         <f>E30-VLOOKUP(A30,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J30" s="22">
+      <c r="J30">
         <f>F30-VLOOKUP(A30,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -7119,15 +7119,15 @@
         <v>46137</v>
       </c>
       <c r="F31" s="5"/>
-      <c r="H31" s="22">
+      <c r="H31">
         <f>D31-VLOOKUP(A31,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I31" s="22">
+      <c r="I31">
         <f>E31-VLOOKUP(A31,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J31" s="22">
+      <c r="J31">
         <f>F31-VLOOKUP(A31,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -7154,15 +7154,15 @@
       <c r="G32" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="H32" s="22">
+      <c r="H32">
         <f>D32-VLOOKUP(A32,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I32" s="23">
+      <c r="I32" s="22">
         <f>E32-VLOOKUP(A32,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J32" s="22">
+      <c r="J32">
         <f>F32-VLOOKUP(A32,'26035'!A:F,6,0)</f>
         <v>46127</v>
       </c>
@@ -7190,15 +7190,15 @@
       <c r="G33" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="H33" s="22">
+      <c r="H33">
         <f>D33-VLOOKUP(A33,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I33" s="23">
+      <c r="I33" s="22">
         <f>E33-VLOOKUP(A33,'26035'!A:F,5,0)</f>
         <v>-5</v>
       </c>
-      <c r="J33" s="22">
+      <c r="J33">
         <f>F33-VLOOKUP(A33,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -7226,15 +7226,15 @@
       <c r="G34" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="H34" s="22">
+      <c r="H34">
         <f>D34-VLOOKUP(A34,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I34" s="22">
+      <c r="I34">
         <f>E34-VLOOKUP(A34,'26035'!A:F,5,0)</f>
         <v>-5</v>
       </c>
-      <c r="J34" s="22">
+      <c r="J34">
         <f>F34-VLOOKUP(A34,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -7256,15 +7256,15 @@
         <v>46143</v>
       </c>
       <c r="F35" s="5"/>
-      <c r="H35" s="22">
+      <c r="H35">
         <f>D35-VLOOKUP(A35,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I35" s="22">
+      <c r="I35">
         <f>E35-VLOOKUP(A35,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J35" s="22">
+      <c r="J35">
         <f>F35-VLOOKUP(A35,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -7289,15 +7289,15 @@
       <c r="G36" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="H36" s="22">
+      <c r="H36">
         <f>D36-VLOOKUP(A36,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I36" s="22">
+      <c r="I36">
         <f>E36-VLOOKUP(A36,'26035'!A:F,5,0)</f>
         <v>-5</v>
       </c>
-      <c r="J36" s="22">
+      <c r="J36">
         <f>F36-VLOOKUP(A36,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -7319,15 +7319,15 @@
         <v>46134</v>
       </c>
       <c r="F37" s="5"/>
-      <c r="H37" s="22">
+      <c r="H37">
         <f>D37-VLOOKUP(A37,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I37" s="22">
+      <c r="I37">
         <f>E37-VLOOKUP(A37,'26035'!A:F,5,0)</f>
         <v>-5</v>
       </c>
-      <c r="J37" s="22">
+      <c r="J37">
         <f>F37-VLOOKUP(A37,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -7349,15 +7349,15 @@
         <v>46134</v>
       </c>
       <c r="F38" s="5"/>
-      <c r="H38" s="22">
+      <c r="H38">
         <f>D38-VLOOKUP(A38,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I38" s="22">
+      <c r="I38">
         <f>E38-VLOOKUP(A38,'26035'!A:F,5,0)</f>
         <v>-5</v>
       </c>
-      <c r="J38" s="22">
+      <c r="J38">
         <f>F38-VLOOKUP(A38,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -7379,15 +7379,15 @@
         <v>46134</v>
       </c>
       <c r="F39" s="5"/>
-      <c r="H39" s="22">
+      <c r="H39">
         <f>D39-VLOOKUP(A39,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I39" s="22">
+      <c r="I39">
         <f>E39-VLOOKUP(A39,'26035'!A:F,5,0)</f>
         <v>-5</v>
       </c>
-      <c r="J39" s="22">
+      <c r="J39">
         <f>F39-VLOOKUP(A39,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -7409,15 +7409,15 @@
         <v>46134</v>
       </c>
       <c r="F40" s="5"/>
-      <c r="H40" s="22">
+      <c r="H40">
         <f>D40-VLOOKUP(A40,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I40" s="22">
+      <c r="I40">
         <f>E40-VLOOKUP(A40,'26035'!A:F,5,0)</f>
         <v>-5</v>
       </c>
-      <c r="J40" s="22">
+      <c r="J40">
         <f>F40-VLOOKUP(A40,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -7439,15 +7439,15 @@
         <v>46134</v>
       </c>
       <c r="F41" s="5"/>
-      <c r="H41" s="22">
+      <c r="H41">
         <f>D41-VLOOKUP(A41,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I41" s="22">
+      <c r="I41">
         <f>E41-VLOOKUP(A41,'26035'!A:F,5,0)</f>
         <v>-5</v>
       </c>
-      <c r="J41" s="22">
+      <c r="J41">
         <f>F41-VLOOKUP(A41,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -7469,15 +7469,15 @@
         <v>46134</v>
       </c>
       <c r="F42" s="5"/>
-      <c r="H42" s="22">
+      <c r="H42">
         <f>D42-VLOOKUP(A42,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I42" s="22">
+      <c r="I42">
         <f>E42-VLOOKUP(A42,'26035'!A:F,5,0)</f>
         <v>-5</v>
       </c>
-      <c r="J42" s="22">
+      <c r="J42">
         <f>F42-VLOOKUP(A42,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -7502,15 +7502,15 @@
       <c r="G43" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="H43" s="22">
+      <c r="H43">
         <f>D43-VLOOKUP(A43,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I43" s="22">
+      <c r="I43">
         <f>E43-VLOOKUP(A43,'26035'!A:F,5,0)</f>
         <v>-5</v>
       </c>
-      <c r="J43" s="22">
+      <c r="J43">
         <f>F43-VLOOKUP(A43,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -7532,15 +7532,15 @@
         <v>46142</v>
       </c>
       <c r="F44" s="8"/>
-      <c r="H44" s="22">
+      <c r="H44">
         <f>D44-VLOOKUP(A44,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I44" s="23">
+      <c r="I44" s="22">
         <f>E44-VLOOKUP(A44,'26035'!A:F,5,0)</f>
         <v>-5</v>
       </c>
-      <c r="J44" s="22">
+      <c r="J44">
         <f>F44-VLOOKUP(A44,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -7565,15 +7565,15 @@
         <v>46142</v>
       </c>
       <c r="F45" s="5"/>
-      <c r="H45" s="22">
+      <c r="H45">
         <f>D45-VLOOKUP(A45,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I45" s="22">
+      <c r="I45">
         <f>E45-VLOOKUP(A45,'26035'!A:F,5,0)</f>
         <v>-5</v>
       </c>
-      <c r="J45" s="22">
+      <c r="J45">
         <f>F45-VLOOKUP(A45,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -7595,15 +7595,15 @@
         <v>46142</v>
       </c>
       <c r="F46" s="5"/>
-      <c r="H46" s="22">
+      <c r="H46">
         <f>D46-VLOOKUP(A46,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I46" s="22">
+      <c r="I46">
         <f>E46-VLOOKUP(A46,'26035'!A:F,5,0)</f>
         <v>-5</v>
       </c>
-      <c r="J46" s="22">
+      <c r="J46">
         <f>F46-VLOOKUP(A46,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -7625,15 +7625,15 @@
         <v>46142</v>
       </c>
       <c r="F47" s="5"/>
-      <c r="H47" s="22">
+      <c r="H47">
         <f>D47-VLOOKUP(A47,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I47" s="22">
+      <c r="I47">
         <f>E47-VLOOKUP(A47,'26035'!A:F,5,0)</f>
         <v>-5</v>
       </c>
-      <c r="J47" s="22">
+      <c r="J47">
         <f>F47-VLOOKUP(A47,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -7655,15 +7655,15 @@
         <v>46142</v>
       </c>
       <c r="F48" s="5"/>
-      <c r="H48" s="22">
+      <c r="H48">
         <f>D48-VLOOKUP(A48,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I48" s="22">
+      <c r="I48">
         <f>E48-VLOOKUP(A48,'26035'!A:F,5,0)</f>
         <v>-5</v>
       </c>
-      <c r="J48" s="22">
+      <c r="J48">
         <f>F48-VLOOKUP(A48,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -7685,15 +7685,15 @@
         <v>46142</v>
       </c>
       <c r="F49" s="5"/>
-      <c r="H49" s="22">
+      <c r="H49">
         <f>D49-VLOOKUP(A49,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I49" s="22">
+      <c r="I49">
         <f>E49-VLOOKUP(A49,'26035'!A:F,5,0)</f>
         <v>-5</v>
       </c>
-      <c r="J49" s="22">
+      <c r="J49">
         <f>F49-VLOOKUP(A49,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -7715,15 +7715,15 @@
         <v>46142</v>
       </c>
       <c r="F50" s="5"/>
-      <c r="H50" s="22">
+      <c r="H50">
         <f>D50-VLOOKUP(A50,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I50" s="22">
+      <c r="I50">
         <f>E50-VLOOKUP(A50,'26035'!A:F,5,0)</f>
         <v>-5</v>
       </c>
-      <c r="J50" s="22">
+      <c r="J50">
         <f>F50-VLOOKUP(A50,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -7745,15 +7745,15 @@
         <v>46156</v>
       </c>
       <c r="F51" s="5"/>
-      <c r="H51" s="22">
+      <c r="H51">
         <f>D51-VLOOKUP(A51,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I51" s="22">
+      <c r="I51">
         <f>E51-VLOOKUP(A51,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J51" s="22">
+      <c r="J51">
         <f>F51-VLOOKUP(A51,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -7777,15 +7777,15 @@
       <c r="F52" s="6">
         <v>46128</v>
       </c>
-      <c r="H52" s="22">
+      <c r="H52">
         <f>D52-VLOOKUP(A52,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I52" s="22">
+      <c r="I52">
         <f>E52-VLOOKUP(A52,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J52" s="22">
+      <c r="J52">
         <f>F52-VLOOKUP(A52,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -7807,15 +7807,15 @@
         <v>46154</v>
       </c>
       <c r="F53" s="5"/>
-      <c r="H53" s="22">
+      <c r="H53">
         <f>D53-VLOOKUP(A53,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I53" s="22">
+      <c r="I53">
         <f>E53-VLOOKUP(A53,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J53" s="22">
+      <c r="J53">
         <f>F53-VLOOKUP(A53,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -7840,15 +7840,15 @@
       <c r="G54" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="H54" s="22">
+      <c r="H54">
         <f>D54-VLOOKUP(A54,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I54" s="22">
+      <c r="I54">
         <f>E54-VLOOKUP(A54,'26035'!A:F,5,0)</f>
         <v>-5</v>
       </c>
-      <c r="J54" s="22">
+      <c r="J54">
         <f>F54-VLOOKUP(A54,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -7873,15 +7873,15 @@
       <c r="G55" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="H55" s="22">
+      <c r="H55">
         <f>D55-VLOOKUP(A55,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I55" s="22">
+      <c r="I55">
         <f>E55-VLOOKUP(A55,'26035'!A:F,5,0)</f>
         <v>-5</v>
       </c>
-      <c r="J55" s="22">
+      <c r="J55">
         <f>F55-VLOOKUP(A55,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -7906,15 +7906,15 @@
       <c r="G56" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="H56" s="22">
+      <c r="H56">
         <f>D56-VLOOKUP(A56,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I56" s="22">
+      <c r="I56">
         <f>E56-VLOOKUP(A56,'26035'!A:F,5,0)</f>
         <v>-5</v>
       </c>
-      <c r="J56" s="22">
+      <c r="J56">
         <f>F56-VLOOKUP(A56,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -7936,15 +7936,15 @@
         <v>46171</v>
       </c>
       <c r="F57" s="5"/>
-      <c r="H57" s="22">
+      <c r="H57">
         <f>D57-VLOOKUP(A57,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I57" s="22">
+      <c r="I57">
         <f>E57-VLOOKUP(A57,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J57" s="22">
+      <c r="J57">
         <f>F57-VLOOKUP(A57,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -7966,15 +7966,15 @@
         <v>46096</v>
       </c>
       <c r="F58" s="11"/>
-      <c r="H58" s="22">
+      <c r="H58">
         <f>D58-VLOOKUP(A58,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I58" s="22">
+      <c r="I58">
         <f>E58-VLOOKUP(A58,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J58" s="22">
+      <c r="J58">
         <f>F58-VLOOKUP(A58,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -7987,7 +7987,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C011C10A-BF9B-4213-99F8-583DC597D3B2}">
-  <sheetPr>
+  <sheetPr codeName="Sheet5">
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
   <dimension ref="A1:J58"/>
@@ -8000,8 +8000,8 @@
     <col min="5" max="5" width="21.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="17.42578125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.42578125" style="13" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.5703125" style="22" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="11.85546875" style="22" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="11.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -8026,13 +8026,13 @@
       <c r="G1" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="H1" s="22" t="s">
+      <c r="H1" t="s">
         <v>110</v>
       </c>
-      <c r="I1" s="22" t="s">
+      <c r="I1" t="s">
         <v>111</v>
       </c>
-      <c r="J1" s="22" t="s">
+      <c r="J1" t="s">
         <v>112</v>
       </c>
     </row>
@@ -8053,15 +8053,15 @@
         <v>46089</v>
       </c>
       <c r="F2" s="2"/>
-      <c r="H2" s="22">
+      <c r="H2">
         <f>D2-VLOOKUP(A2,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I2" s="22">
+      <c r="I2">
         <f>E2-VLOOKUP(A2,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J2" s="22">
+      <c r="J2">
         <f>F2-VLOOKUP(A2,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -8083,15 +8083,15 @@
         <v>46094</v>
       </c>
       <c r="F3" s="5"/>
-      <c r="H3" s="22">
+      <c r="H3">
         <f>D3-VLOOKUP(A3,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I3" s="22">
+      <c r="I3">
         <f>E3-VLOOKUP(A3,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J3" s="22">
+      <c r="J3">
         <f>F3-VLOOKUP(A3,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -8118,15 +8118,15 @@
       <c r="G4" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="H4" s="22">
+      <c r="H4">
         <f>D4-VLOOKUP(A4,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I4" s="22">
+      <c r="I4">
         <f>E4-VLOOKUP(A4,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J4" s="22">
+      <c r="J4">
         <f>F4-VLOOKUP(A4,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -8148,15 +8148,15 @@
         <v>46103</v>
       </c>
       <c r="F5" s="5"/>
-      <c r="H5" s="22">
+      <c r="H5">
         <f>D5-VLOOKUP(A5,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I5" s="22">
+      <c r="I5">
         <f>E5-VLOOKUP(A5,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J5" s="22">
+      <c r="J5">
         <f>F5-VLOOKUP(A5,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -8178,15 +8178,15 @@
         <v>46107</v>
       </c>
       <c r="F6" s="5"/>
-      <c r="H6" s="22">
+      <c r="H6">
         <f>D6-VLOOKUP(A6,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I6" s="22">
+      <c r="I6">
         <f>E6-VLOOKUP(A6,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J6" s="22">
+      <c r="J6">
         <f>F6-VLOOKUP(A6,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -8208,15 +8208,15 @@
         <v>46114</v>
       </c>
       <c r="F7" s="5"/>
-      <c r="H7" s="22">
+      <c r="H7">
         <f>D7-VLOOKUP(A7,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I7" s="22">
+      <c r="I7">
         <f>E7-VLOOKUP(A7,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J7" s="22">
+      <c r="J7">
         <f>F7-VLOOKUP(A7,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -8238,15 +8238,15 @@
         <v>46109</v>
       </c>
       <c r="F8" s="5"/>
-      <c r="H8" s="22">
+      <c r="H8">
         <f>D8-VLOOKUP(A8,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I8" s="22">
+      <c r="I8">
         <f>E8-VLOOKUP(A8,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J8" s="22">
+      <c r="J8">
         <f>F8-VLOOKUP(A8,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -8268,15 +8268,15 @@
         <v>46109</v>
       </c>
       <c r="F9" s="5"/>
-      <c r="H9" s="22">
+      <c r="H9">
         <f>D9-VLOOKUP(A9,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I9" s="22">
+      <c r="I9">
         <f>E9-VLOOKUP(A9,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J9" s="22">
+      <c r="J9">
         <f>F9-VLOOKUP(A9,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -8298,15 +8298,15 @@
         <v>46109</v>
       </c>
       <c r="F10" s="5"/>
-      <c r="H10" s="22">
+      <c r="H10">
         <f>D10-VLOOKUP(A10,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I10" s="22">
+      <c r="I10">
         <f>E10-VLOOKUP(A10,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J10" s="22">
+      <c r="J10">
         <f>F10-VLOOKUP(A10,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -8328,15 +8328,15 @@
         <v>46109</v>
       </c>
       <c r="F11" s="5"/>
-      <c r="H11" s="22">
+      <c r="H11">
         <f>D11-VLOOKUP(A11,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I11" s="22">
+      <c r="I11">
         <f>E11-VLOOKUP(A11,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J11" s="22">
+      <c r="J11">
         <f>F11-VLOOKUP(A11,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -8358,15 +8358,15 @@
         <v>46109</v>
       </c>
       <c r="F12" s="5"/>
-      <c r="H12" s="22">
+      <c r="H12">
         <f>D12-VLOOKUP(A12,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I12" s="22">
+      <c r="I12">
         <f>E12-VLOOKUP(A12,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J12" s="22">
+      <c r="J12">
         <f>F12-VLOOKUP(A12,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -8388,15 +8388,15 @@
         <v>46109</v>
       </c>
       <c r="F13" s="5"/>
-      <c r="H13" s="22">
+      <c r="H13">
         <f>D13-VLOOKUP(A13,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I13" s="22">
+      <c r="I13">
         <f>E13-VLOOKUP(A13,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J13" s="22">
+      <c r="J13">
         <f>F13-VLOOKUP(A13,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -8418,15 +8418,15 @@
         <v>46109</v>
       </c>
       <c r="F14" s="5"/>
-      <c r="H14" s="22">
+      <c r="H14">
         <f>D14-VLOOKUP(A14,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I14" s="22">
+      <c r="I14">
         <f>E14-VLOOKUP(A14,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J14" s="22">
+      <c r="J14">
         <f>F14-VLOOKUP(A14,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -8448,15 +8448,15 @@
         <v>46109</v>
       </c>
       <c r="F15" s="5"/>
-      <c r="H15" s="22">
+      <c r="H15">
         <f>D15-VLOOKUP(A15,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I15" s="22">
+      <c r="I15">
         <f>E15-VLOOKUP(A15,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J15" s="22">
+      <c r="J15">
         <f>F15-VLOOKUP(A15,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -8478,15 +8478,15 @@
         <v>46108</v>
       </c>
       <c r="F16" s="5"/>
-      <c r="H16" s="22">
+      <c r="H16">
         <f>D16-VLOOKUP(A16,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I16" s="22">
+      <c r="I16">
         <f>E16-VLOOKUP(A16,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J16" s="22">
+      <c r="J16">
         <f>F16-VLOOKUP(A16,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -8508,15 +8508,15 @@
         <v>46109</v>
       </c>
       <c r="F17" s="5"/>
-      <c r="H17" s="22">
+      <c r="H17">
         <f>D17-VLOOKUP(A17,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I17" s="22">
+      <c r="I17">
         <f>E17-VLOOKUP(A17,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J17" s="22">
+      <c r="J17">
         <f>F17-VLOOKUP(A17,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -8538,15 +8538,15 @@
         <v>46115</v>
       </c>
       <c r="F18" s="5"/>
-      <c r="H18" s="22">
+      <c r="H18">
         <f>D18-VLOOKUP(A18,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I18" s="22">
+      <c r="I18">
         <f>E18-VLOOKUP(A18,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J18" s="22">
+      <c r="J18">
         <f>F18-VLOOKUP(A18,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -8571,15 +8571,15 @@
       <c r="G19" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="H19" s="22">
+      <c r="H19">
         <f>D19-VLOOKUP(A19,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I19" s="22">
+      <c r="I19">
         <f>E19-VLOOKUP(A19,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J19" s="22">
+      <c r="J19">
         <f>F19-VLOOKUP(A19,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -8601,15 +8601,15 @@
         <v>46108</v>
       </c>
       <c r="F20" s="5"/>
-      <c r="H20" s="22">
+      <c r="H20">
         <f>D20-VLOOKUP(A20,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I20" s="22">
+      <c r="I20">
         <f>E20-VLOOKUP(A20,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J20" s="22">
+      <c r="J20">
         <f>F20-VLOOKUP(A20,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -8631,15 +8631,15 @@
         <v>46108</v>
       </c>
       <c r="F21" s="5"/>
-      <c r="H21" s="22">
+      <c r="H21">
         <f>D21-VLOOKUP(A21,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I21" s="22">
+      <c r="I21">
         <f>E21-VLOOKUP(A21,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J21" s="22">
+      <c r="J21">
         <f>F21-VLOOKUP(A21,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -8661,15 +8661,15 @@
         <v>46108</v>
       </c>
       <c r="F22" s="5"/>
-      <c r="H22" s="22">
+      <c r="H22">
         <f>D22-VLOOKUP(A22,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I22" s="22">
+      <c r="I22">
         <f>E22-VLOOKUP(A22,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J22" s="22">
+      <c r="J22">
         <f>F22-VLOOKUP(A22,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -8691,15 +8691,15 @@
         <v>46108</v>
       </c>
       <c r="F23" s="5"/>
-      <c r="H23" s="22">
+      <c r="H23">
         <f>D23-VLOOKUP(A23,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I23" s="22">
+      <c r="I23">
         <f>E23-VLOOKUP(A23,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J23" s="22">
+      <c r="J23">
         <f>F23-VLOOKUP(A23,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -8721,15 +8721,15 @@
         <v>46108</v>
       </c>
       <c r="F24" s="5"/>
-      <c r="H24" s="22">
+      <c r="H24">
         <f>D24-VLOOKUP(A24,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I24" s="22">
+      <c r="I24">
         <f>E24-VLOOKUP(A24,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J24" s="22">
+      <c r="J24">
         <f>F24-VLOOKUP(A24,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -8751,15 +8751,15 @@
         <v>46108</v>
       </c>
       <c r="F25" s="5"/>
-      <c r="H25" s="22">
+      <c r="H25">
         <f>D25-VLOOKUP(A25,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I25" s="22">
+      <c r="I25">
         <f>E25-VLOOKUP(A25,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J25" s="22">
+      <c r="J25">
         <f>F25-VLOOKUP(A25,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -8781,15 +8781,15 @@
         <v>46104</v>
       </c>
       <c r="F26" s="5"/>
-      <c r="H26" s="22">
+      <c r="H26">
         <f>D26-VLOOKUP(A26,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I26" s="22">
+      <c r="I26">
         <f>E26-VLOOKUP(A26,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J26" s="22">
+      <c r="J26">
         <f>F26-VLOOKUP(A26,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -8811,15 +8811,15 @@
         <v>46113</v>
       </c>
       <c r="F27" s="5"/>
-      <c r="H27" s="22">
+      <c r="H27">
         <f>D27-VLOOKUP(A27,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I27" s="22">
+      <c r="I27">
         <f>E27-VLOOKUP(A27,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J27" s="22">
+      <c r="J27">
         <f>F27-VLOOKUP(A27,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -8841,15 +8841,15 @@
         <v>46114</v>
       </c>
       <c r="F28" s="5"/>
-      <c r="H28" s="22">
+      <c r="H28">
         <f>D28-VLOOKUP(A28,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I28" s="22">
+      <c r="I28">
         <f>E28-VLOOKUP(A28,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J28" s="22">
+      <c r="J28">
         <f>F28-VLOOKUP(A28,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -8871,15 +8871,15 @@
         <v>46118</v>
       </c>
       <c r="F29" s="5"/>
-      <c r="H29" s="22">
+      <c r="H29">
         <f>D29-VLOOKUP(A29,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I29" s="22">
+      <c r="I29">
         <f>E29-VLOOKUP(A29,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J29" s="22">
+      <c r="J29">
         <f>F29-VLOOKUP(A29,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -8901,15 +8901,15 @@
         <v>46124</v>
       </c>
       <c r="F30" s="5"/>
-      <c r="H30" s="22">
+      <c r="H30">
         <f>D30-VLOOKUP(A30,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I30" s="22">
+      <c r="I30">
         <f>E30-VLOOKUP(A30,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J30" s="22">
+      <c r="J30">
         <f>F30-VLOOKUP(A30,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -8931,15 +8931,15 @@
         <v>46137</v>
       </c>
       <c r="F31" s="5"/>
-      <c r="H31" s="22">
+      <c r="H31">
         <f>D31-VLOOKUP(A31,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I31" s="22">
+      <c r="I31">
         <f>E31-VLOOKUP(A31,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J31" s="22">
+      <c r="J31">
         <f>F31-VLOOKUP(A31,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -8966,15 +8966,15 @@
       <c r="G32" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="H32" s="22">
+      <c r="H32">
         <f>D32-VLOOKUP(A32,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I32" s="28">
+      <c r="I32">
         <f>E32-VLOOKUP(A32,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J32" s="22">
+      <c r="J32">
         <f>F32-VLOOKUP(A32,'26035'!A:F,6,0)</f>
         <v>46127</v>
       </c>
@@ -8999,15 +8999,15 @@
       <c r="G33" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="H33" s="22">
+      <c r="H33">
         <f>D33-VLOOKUP(A33,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I33" s="28">
+      <c r="I33">
         <f>E33-VLOOKUP(A33,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J33" s="22">
+      <c r="J33">
         <f>F33-VLOOKUP(A33,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -9032,15 +9032,15 @@
       <c r="G34" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="H34" s="22">
+      <c r="H34">
         <f>D34-VLOOKUP(A34,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I34" s="28">
+      <c r="I34">
         <f>E34-VLOOKUP(A34,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J34" s="22">
+      <c r="J34">
         <f>F34-VLOOKUP(A34,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -9062,15 +9062,15 @@
         <v>46143</v>
       </c>
       <c r="F35" s="5"/>
-      <c r="H35" s="22">
+      <c r="H35">
         <f>D35-VLOOKUP(A35,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I35" s="28">
+      <c r="I35">
         <f>E35-VLOOKUP(A35,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J35" s="22">
+      <c r="J35">
         <f>F35-VLOOKUP(A35,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -9095,15 +9095,15 @@
       <c r="G36" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="H36" s="22">
+      <c r="H36">
         <f>D36-VLOOKUP(A36,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I36" s="28">
+      <c r="I36">
         <f>E36-VLOOKUP(A36,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J36" s="22">
+      <c r="J36">
         <f>F36-VLOOKUP(A36,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -9125,15 +9125,15 @@
         <v>46139</v>
       </c>
       <c r="F37" s="5"/>
-      <c r="H37" s="22">
+      <c r="H37">
         <f>D37-VLOOKUP(A37,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I37" s="28">
+      <c r="I37">
         <f>E37-VLOOKUP(A37,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J37" s="22">
+      <c r="J37">
         <f>F37-VLOOKUP(A37,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -9155,15 +9155,15 @@
         <v>46139</v>
       </c>
       <c r="F38" s="5"/>
-      <c r="H38" s="22">
+      <c r="H38">
         <f>D38-VLOOKUP(A38,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I38" s="28">
+      <c r="I38">
         <f>E38-VLOOKUP(A38,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J38" s="22">
+      <c r="J38">
         <f>F38-VLOOKUP(A38,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -9185,15 +9185,15 @@
         <v>46139</v>
       </c>
       <c r="F39" s="5"/>
-      <c r="H39" s="22">
+      <c r="H39">
         <f>D39-VLOOKUP(A39,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I39" s="28">
+      <c r="I39">
         <f>E39-VLOOKUP(A39,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J39" s="22">
+      <c r="J39">
         <f>F39-VLOOKUP(A39,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -9215,15 +9215,15 @@
         <v>46139</v>
       </c>
       <c r="F40" s="5"/>
-      <c r="H40" s="22">
+      <c r="H40">
         <f>D40-VLOOKUP(A40,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I40" s="28">
+      <c r="I40">
         <f>E40-VLOOKUP(A40,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J40" s="22">
+      <c r="J40">
         <f>F40-VLOOKUP(A40,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -9245,15 +9245,15 @@
         <v>46139</v>
       </c>
       <c r="F41" s="5"/>
-      <c r="H41" s="22">
+      <c r="H41">
         <f>D41-VLOOKUP(A41,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I41" s="28">
+      <c r="I41">
         <f>E41-VLOOKUP(A41,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J41" s="22">
+      <c r="J41">
         <f>F41-VLOOKUP(A41,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -9275,15 +9275,15 @@
         <v>46139</v>
       </c>
       <c r="F42" s="5"/>
-      <c r="H42" s="22">
+      <c r="H42">
         <f>D42-VLOOKUP(A42,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I42" s="28">
+      <c r="I42">
         <f>E42-VLOOKUP(A42,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J42" s="22">
+      <c r="J42">
         <f>F42-VLOOKUP(A42,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -9308,15 +9308,15 @@
       <c r="G43" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="H43" s="22">
+      <c r="H43">
         <f>D43-VLOOKUP(A43,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I43" s="28">
+      <c r="I43">
         <f>E43-VLOOKUP(A43,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J43" s="22">
+      <c r="J43">
         <f>F43-VLOOKUP(A43,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -9338,15 +9338,15 @@
         <v>46147</v>
       </c>
       <c r="F44" s="8"/>
-      <c r="H44" s="22">
+      <c r="H44">
         <f>D44-VLOOKUP(A44,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I44" s="28">
+      <c r="I44">
         <f>E44-VLOOKUP(A44,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J44" s="22">
+      <c r="J44">
         <f>F44-VLOOKUP(A44,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -9368,46 +9368,46 @@
         <v>46147</v>
       </c>
       <c r="F45" s="5"/>
-      <c r="H45" s="22">
+      <c r="H45">
         <f>D45-VLOOKUP(A45,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I45" s="22">
+      <c r="I45">
         <f>E45-VLOOKUP(A45,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J45" s="22">
+      <c r="J45">
         <f>F45-VLOOKUP(A45,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="24" t="s">
+      <c r="A46" s="23" t="s">
         <v>76</v>
       </c>
-      <c r="B46" s="25" t="s">
+      <c r="B46" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="C46" s="25" t="s">
+      <c r="C46" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="D46" s="26">
+      <c r="D46" s="25">
         <v>46147</v>
       </c>
-      <c r="E46" s="26">
+      <c r="E46" s="25">
         <v>46147</v>
       </c>
-      <c r="F46" s="25"/>
-      <c r="G46" s="27"/>
-      <c r="H46" s="23">
+      <c r="F46" s="24"/>
+      <c r="G46" s="26"/>
+      <c r="H46" s="22">
         <f>D46-VLOOKUP(A46,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I46" s="23">
+      <c r="I46" s="22">
         <f>E46-VLOOKUP(A46,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J46" s="23">
+      <c r="J46" s="22">
         <f>F46-VLOOKUP(A46,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -9429,15 +9429,15 @@
         <v>46147</v>
       </c>
       <c r="F47" s="5"/>
-      <c r="H47" s="22">
+      <c r="H47">
         <f>D47-VLOOKUP(A47,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I47" s="22">
+      <c r="I47">
         <f>E47-VLOOKUP(A47,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J47" s="22">
+      <c r="J47">
         <f>F47-VLOOKUP(A47,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -9459,15 +9459,15 @@
         <v>46147</v>
       </c>
       <c r="F48" s="5"/>
-      <c r="H48" s="22">
+      <c r="H48">
         <f>D48-VLOOKUP(A48,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I48" s="22">
+      <c r="I48">
         <f>E48-VLOOKUP(A48,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J48" s="22">
+      <c r="J48">
         <f>F48-VLOOKUP(A48,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -9489,15 +9489,15 @@
         <v>46147</v>
       </c>
       <c r="F49" s="5"/>
-      <c r="H49" s="22">
+      <c r="H49">
         <f>D49-VLOOKUP(A49,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I49" s="22">
+      <c r="I49">
         <f>E49-VLOOKUP(A49,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J49" s="22">
+      <c r="J49">
         <f>F49-VLOOKUP(A49,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -9519,15 +9519,15 @@
         <v>46147</v>
       </c>
       <c r="F50" s="5"/>
-      <c r="H50" s="22">
+      <c r="H50">
         <f>D50-VLOOKUP(A50,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I50" s="22">
+      <c r="I50">
         <f>E50-VLOOKUP(A50,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J50" s="22">
+      <c r="J50">
         <f>F50-VLOOKUP(A50,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -9549,15 +9549,15 @@
         <v>46156</v>
       </c>
       <c r="F51" s="5"/>
-      <c r="H51" s="22">
+      <c r="H51">
         <f>D51-VLOOKUP(A51,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I51" s="22">
+      <c r="I51">
         <f>E51-VLOOKUP(A51,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J51" s="22">
+      <c r="J51">
         <f>F51-VLOOKUP(A51,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -9581,15 +9581,15 @@
       <c r="F52" s="6">
         <v>46128</v>
       </c>
-      <c r="H52" s="22">
+      <c r="H52">
         <f>D52-VLOOKUP(A52,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I52" s="22">
+      <c r="I52">
         <f>E52-VLOOKUP(A52,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J52" s="22">
+      <c r="J52">
         <f>F52-VLOOKUP(A52,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -9611,15 +9611,15 @@
         <v>46154</v>
       </c>
       <c r="F53" s="5"/>
-      <c r="H53" s="22">
+      <c r="H53">
         <f>D53-VLOOKUP(A53,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I53" s="22">
+      <c r="I53">
         <f>E53-VLOOKUP(A53,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J53" s="22">
+      <c r="J53">
         <f>F53-VLOOKUP(A53,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -9644,15 +9644,15 @@
       <c r="G54" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="H54" s="22">
+      <c r="H54">
         <f>D54-VLOOKUP(A54,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I54" s="22">
+      <c r="I54">
         <f>E54-VLOOKUP(A54,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J54" s="22">
+      <c r="J54">
         <f>F54-VLOOKUP(A54,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -9677,15 +9677,15 @@
       <c r="G55" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="H55" s="22">
+      <c r="H55">
         <f>D55-VLOOKUP(A55,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I55" s="22">
+      <c r="I55">
         <f>E55-VLOOKUP(A55,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J55" s="22">
+      <c r="J55">
         <f>F55-VLOOKUP(A55,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -9710,15 +9710,15 @@
       <c r="G56" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="H56" s="22">
+      <c r="H56">
         <f>D56-VLOOKUP(A56,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I56" s="22">
+      <c r="I56">
         <f>E56-VLOOKUP(A56,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J56" s="22">
+      <c r="J56">
         <f>F56-VLOOKUP(A56,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -9740,15 +9740,15 @@
         <v>46171</v>
       </c>
       <c r="F57" s="5"/>
-      <c r="H57" s="22">
+      <c r="H57">
         <f>D57-VLOOKUP(A57,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I57" s="22">
+      <c r="I57">
         <f>E57-VLOOKUP(A57,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J57" s="22">
+      <c r="J57">
         <f>F57-VLOOKUP(A57,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -9770,15 +9770,15 @@
         <v>46096</v>
       </c>
       <c r="F58" s="11"/>
-      <c r="H58" s="22">
+      <c r="H58">
         <f>D58-VLOOKUP(A58,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I58" s="22">
+      <c r="I58">
         <f>E58-VLOOKUP(A58,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J58" s="22">
+      <c r="J58">
         <f>F58-VLOOKUP(A58,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -9791,6 +9791,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E38C69C7-7461-47E4-A3FB-1E619F276F01}">
+  <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:J58"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -9801,8 +9802,8 @@
     <col min="5" max="5" width="21.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="17.42578125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.42578125" style="13" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.5703125" style="22" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="11.85546875" style="22" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="11.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -9827,13 +9828,13 @@
       <c r="G1" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="H1" s="22" t="s">
+      <c r="H1" t="s">
         <v>110</v>
       </c>
-      <c r="I1" s="22" t="s">
+      <c r="I1" t="s">
         <v>111</v>
       </c>
-      <c r="J1" s="22" t="s">
+      <c r="J1" t="s">
         <v>112</v>
       </c>
     </row>
@@ -9854,15 +9855,15 @@
         <v>46089</v>
       </c>
       <c r="F2" s="2"/>
-      <c r="H2" s="22">
+      <c r="H2">
         <f>D2-VLOOKUP(A2,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I2" s="22">
+      <c r="I2">
         <f>E2-VLOOKUP(A2,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J2" s="22">
+      <c r="J2">
         <f>F2-VLOOKUP(A2,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -9884,15 +9885,15 @@
         <v>46094</v>
       </c>
       <c r="F3" s="5"/>
-      <c r="H3" s="22">
+      <c r="H3">
         <f>D3-VLOOKUP(A3,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I3" s="22">
+      <c r="I3">
         <f>E3-VLOOKUP(A3,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J3" s="22">
+      <c r="J3">
         <f>F3-VLOOKUP(A3,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -9919,15 +9920,15 @@
       <c r="G4" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="H4" s="22">
+      <c r="H4">
         <f>D4-VLOOKUP(A4,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I4" s="22">
+      <c r="I4">
         <f>E4-VLOOKUP(A4,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J4" s="22">
+      <c r="J4">
         <f>F4-VLOOKUP(A4,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -9949,15 +9950,15 @@
         <v>46103</v>
       </c>
       <c r="F5" s="5"/>
-      <c r="H5" s="22">
+      <c r="H5">
         <f>D5-VLOOKUP(A5,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I5" s="22">
+      <c r="I5">
         <f>E5-VLOOKUP(A5,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J5" s="22">
+      <c r="J5">
         <f>F5-VLOOKUP(A5,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -9979,15 +9980,15 @@
         <v>46107</v>
       </c>
       <c r="F6" s="5"/>
-      <c r="H6" s="22">
+      <c r="H6">
         <f>D6-VLOOKUP(A6,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I6" s="22">
+      <c r="I6">
         <f>E6-VLOOKUP(A6,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J6" s="22">
+      <c r="J6">
         <f>F6-VLOOKUP(A6,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -10009,15 +10010,15 @@
         <v>46114</v>
       </c>
       <c r="F7" s="5"/>
-      <c r="H7" s="22">
+      <c r="H7">
         <f>D7-VLOOKUP(A7,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I7" s="22">
+      <c r="I7">
         <f>E7-VLOOKUP(A7,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J7" s="22">
+      <c r="J7">
         <f>F7-VLOOKUP(A7,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -10039,15 +10040,15 @@
         <v>46109</v>
       </c>
       <c r="F8" s="5"/>
-      <c r="H8" s="22">
+      <c r="H8">
         <f>D8-VLOOKUP(A8,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I8" s="22">
+      <c r="I8">
         <f>E8-VLOOKUP(A8,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J8" s="22">
+      <c r="J8">
         <f>F8-VLOOKUP(A8,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -10069,15 +10070,15 @@
         <v>46109</v>
       </c>
       <c r="F9" s="5"/>
-      <c r="H9" s="22">
+      <c r="H9">
         <f>D9-VLOOKUP(A9,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I9" s="22">
+      <c r="I9">
         <f>E9-VLOOKUP(A9,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J9" s="22">
+      <c r="J9">
         <f>F9-VLOOKUP(A9,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -10099,15 +10100,15 @@
         <v>46109</v>
       </c>
       <c r="F10" s="5"/>
-      <c r="H10" s="22">
+      <c r="H10">
         <f>D10-VLOOKUP(A10,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I10" s="22">
+      <c r="I10">
         <f>E10-VLOOKUP(A10,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J10" s="22">
+      <c r="J10">
         <f>F10-VLOOKUP(A10,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -10129,15 +10130,15 @@
         <v>46109</v>
       </c>
       <c r="F11" s="5"/>
-      <c r="H11" s="22">
+      <c r="H11">
         <f>D11-VLOOKUP(A11,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I11" s="22">
+      <c r="I11">
         <f>E11-VLOOKUP(A11,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J11" s="22">
+      <c r="J11">
         <f>F11-VLOOKUP(A11,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -10159,15 +10160,15 @@
         <v>46109</v>
       </c>
       <c r="F12" s="5"/>
-      <c r="H12" s="22">
+      <c r="H12">
         <f>D12-VLOOKUP(A12,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I12" s="22">
+      <c r="I12">
         <f>E12-VLOOKUP(A12,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J12" s="22">
+      <c r="J12">
         <f>F12-VLOOKUP(A12,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -10189,15 +10190,15 @@
         <v>46109</v>
       </c>
       <c r="F13" s="5"/>
-      <c r="H13" s="22">
+      <c r="H13">
         <f>D13-VLOOKUP(A13,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I13" s="22">
+      <c r="I13">
         <f>E13-VLOOKUP(A13,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J13" s="22">
+      <c r="J13">
         <f>F13-VLOOKUP(A13,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -10219,15 +10220,15 @@
         <v>46109</v>
       </c>
       <c r="F14" s="5"/>
-      <c r="H14" s="22">
+      <c r="H14">
         <f>D14-VLOOKUP(A14,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I14" s="22">
+      <c r="I14">
         <f>E14-VLOOKUP(A14,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J14" s="22">
+      <c r="J14">
         <f>F14-VLOOKUP(A14,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -10249,15 +10250,15 @@
         <v>46109</v>
       </c>
       <c r="F15" s="5"/>
-      <c r="H15" s="22">
+      <c r="H15">
         <f>D15-VLOOKUP(A15,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I15" s="22">
+      <c r="I15">
         <f>E15-VLOOKUP(A15,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J15" s="22">
+      <c r="J15">
         <f>F15-VLOOKUP(A15,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -10279,15 +10280,15 @@
         <v>46108</v>
       </c>
       <c r="F16" s="5"/>
-      <c r="H16" s="22">
+      <c r="H16">
         <f>D16-VLOOKUP(A16,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I16" s="22">
+      <c r="I16">
         <f>E16-VLOOKUP(A16,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J16" s="22">
+      <c r="J16">
         <f>F16-VLOOKUP(A16,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -10309,15 +10310,15 @@
         <v>46109</v>
       </c>
       <c r="F17" s="5"/>
-      <c r="H17" s="22">
+      <c r="H17">
         <f>D17-VLOOKUP(A17,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I17" s="22">
+      <c r="I17">
         <f>E17-VLOOKUP(A17,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J17" s="22">
+      <c r="J17">
         <f>F17-VLOOKUP(A17,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -10339,15 +10340,15 @@
         <v>46115</v>
       </c>
       <c r="F18" s="5"/>
-      <c r="H18" s="22">
+      <c r="H18">
         <f>D18-VLOOKUP(A18,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I18" s="22">
+      <c r="I18">
         <f>E18-VLOOKUP(A18,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J18" s="22">
+      <c r="J18">
         <f>F18-VLOOKUP(A18,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -10372,15 +10373,15 @@
       <c r="G19" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="H19" s="22">
+      <c r="H19">
         <f>D19-VLOOKUP(A19,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I19" s="22">
+      <c r="I19">
         <f>E19-VLOOKUP(A19,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J19" s="22">
+      <c r="J19">
         <f>F19-VLOOKUP(A19,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -10402,15 +10403,15 @@
         <v>46108</v>
       </c>
       <c r="F20" s="5"/>
-      <c r="H20" s="22">
+      <c r="H20">
         <f>D20-VLOOKUP(A20,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I20" s="22">
+      <c r="I20">
         <f>E20-VLOOKUP(A20,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J20" s="22">
+      <c r="J20">
         <f>F20-VLOOKUP(A20,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -10432,15 +10433,15 @@
         <v>46108</v>
       </c>
       <c r="F21" s="5"/>
-      <c r="H21" s="22">
+      <c r="H21">
         <f>D21-VLOOKUP(A21,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I21" s="22">
+      <c r="I21">
         <f>E21-VLOOKUP(A21,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J21" s="22">
+      <c r="J21">
         <f>F21-VLOOKUP(A21,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -10462,15 +10463,15 @@
         <v>46108</v>
       </c>
       <c r="F22" s="5"/>
-      <c r="H22" s="22">
+      <c r="H22">
         <f>D22-VLOOKUP(A22,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I22" s="22">
+      <c r="I22">
         <f>E22-VLOOKUP(A22,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J22" s="22">
+      <c r="J22">
         <f>F22-VLOOKUP(A22,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -10492,15 +10493,15 @@
         <v>46108</v>
       </c>
       <c r="F23" s="5"/>
-      <c r="H23" s="22">
+      <c r="H23">
         <f>D23-VLOOKUP(A23,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I23" s="22">
+      <c r="I23">
         <f>E23-VLOOKUP(A23,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J23" s="22">
+      <c r="J23">
         <f>F23-VLOOKUP(A23,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -10522,15 +10523,15 @@
         <v>46108</v>
       </c>
       <c r="F24" s="5"/>
-      <c r="H24" s="22">
+      <c r="H24">
         <f>D24-VLOOKUP(A24,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I24" s="22">
+      <c r="I24">
         <f>E24-VLOOKUP(A24,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J24" s="22">
+      <c r="J24">
         <f>F24-VLOOKUP(A24,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -10552,15 +10553,15 @@
         <v>46108</v>
       </c>
       <c r="F25" s="5"/>
-      <c r="H25" s="22">
+      <c r="H25">
         <f>D25-VLOOKUP(A25,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I25" s="22">
+      <c r="I25">
         <f>E25-VLOOKUP(A25,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J25" s="22">
+      <c r="J25">
         <f>F25-VLOOKUP(A25,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -10582,15 +10583,15 @@
         <v>46104</v>
       </c>
       <c r="F26" s="5"/>
-      <c r="H26" s="22">
+      <c r="H26">
         <f>D26-VLOOKUP(A26,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I26" s="22">
+      <c r="I26">
         <f>E26-VLOOKUP(A26,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J26" s="22">
+      <c r="J26">
         <f>F26-VLOOKUP(A26,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -10612,15 +10613,15 @@
         <v>46113</v>
       </c>
       <c r="F27" s="5"/>
-      <c r="H27" s="22">
+      <c r="H27">
         <f>D27-VLOOKUP(A27,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I27" s="22">
+      <c r="I27">
         <f>E27-VLOOKUP(A27,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J27" s="22">
+      <c r="J27">
         <f>F27-VLOOKUP(A27,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -10642,15 +10643,15 @@
         <v>46114</v>
       </c>
       <c r="F28" s="5"/>
-      <c r="H28" s="22">
+      <c r="H28">
         <f>D28-VLOOKUP(A28,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I28" s="22">
+      <c r="I28">
         <f>E28-VLOOKUP(A28,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J28" s="22">
+      <c r="J28">
         <f>F28-VLOOKUP(A28,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -10672,15 +10673,15 @@
         <v>46118</v>
       </c>
       <c r="F29" s="5"/>
-      <c r="H29" s="22">
+      <c r="H29">
         <f>D29-VLOOKUP(A29,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I29" s="22">
+      <c r="I29">
         <f>E29-VLOOKUP(A29,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J29" s="22">
+      <c r="J29">
         <f>F29-VLOOKUP(A29,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -10702,15 +10703,15 @@
         <v>46124</v>
       </c>
       <c r="F30" s="5"/>
-      <c r="H30" s="22">
+      <c r="H30">
         <f>D30-VLOOKUP(A30,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I30" s="22">
+      <c r="I30">
         <f>E30-VLOOKUP(A30,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J30" s="22">
+      <c r="J30">
         <f>F30-VLOOKUP(A30,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -10732,15 +10733,15 @@
         <v>46137</v>
       </c>
       <c r="F31" s="5"/>
-      <c r="H31" s="22">
+      <c r="H31">
         <f>D31-VLOOKUP(A31,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I31" s="22">
+      <c r="I31">
         <f>E31-VLOOKUP(A31,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J31" s="22">
+      <c r="J31">
         <f>F31-VLOOKUP(A31,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -10767,15 +10768,15 @@
       <c r="G32" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="H32" s="22">
+      <c r="H32">
         <f>D32-VLOOKUP(A32,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I32" s="28">
+      <c r="I32">
         <f>E32-VLOOKUP(A32,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J32" s="22">
+      <c r="J32">
         <f>F32-VLOOKUP(A32,'26035'!A:F,6,0)</f>
         <v>46127</v>
       </c>
@@ -10800,15 +10801,15 @@
       <c r="G33" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="H33" s="22">
+      <c r="H33">
         <f>D33-VLOOKUP(A33,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I33" s="28">
+      <c r="I33">
         <f>E33-VLOOKUP(A33,'26035'!A:F,5,0)</f>
         <v>-37</v>
       </c>
-      <c r="J33" s="22">
+      <c r="J33">
         <f>F33-VLOOKUP(A33,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -10833,15 +10834,15 @@
       <c r="G34" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="H34" s="22">
+      <c r="H34">
         <f>D34-VLOOKUP(A34,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I34" s="28">
+      <c r="I34">
         <f>E34-VLOOKUP(A34,'26035'!A:F,5,0)</f>
         <v>-33</v>
       </c>
-      <c r="J34" s="22">
+      <c r="J34">
         <f>F34-VLOOKUP(A34,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -10863,15 +10864,15 @@
         <v>46143</v>
       </c>
       <c r="F35" s="5"/>
-      <c r="H35" s="22">
+      <c r="H35">
         <f>D35-VLOOKUP(A35,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I35" s="28">
+      <c r="I35">
         <f>E35-VLOOKUP(A35,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J35" s="22">
+      <c r="J35">
         <f>F35-VLOOKUP(A35,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -10889,22 +10890,22 @@
       <c r="D36" s="6">
         <v>46143</v>
       </c>
-      <c r="E36" s="29">
+      <c r="E36" s="27">
         <v>46108</v>
       </c>
       <c r="F36" s="5"/>
       <c r="G36" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="H36" s="22">
+      <c r="H36">
         <f>D36-VLOOKUP(A36,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I36" s="28">
+      <c r="I36">
         <f>E36-VLOOKUP(A36,'26035'!A:F,5,0)</f>
         <v>-31</v>
       </c>
-      <c r="J36" s="22">
+      <c r="J36">
         <f>F36-VLOOKUP(A36,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -10922,19 +10923,19 @@
       <c r="D37" s="6">
         <v>46139</v>
       </c>
-      <c r="E37" s="29">
+      <c r="E37" s="27">
         <v>46108</v>
       </c>
       <c r="F37" s="5"/>
-      <c r="H37" s="22">
+      <c r="H37">
         <f>D37-VLOOKUP(A37,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I37" s="28">
+      <c r="I37">
         <f>E37-VLOOKUP(A37,'26035'!A:F,5,0)</f>
         <v>-31</v>
       </c>
-      <c r="J37" s="22">
+      <c r="J37">
         <f>F37-VLOOKUP(A37,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -10952,19 +10953,19 @@
       <c r="D38" s="6">
         <v>46139</v>
       </c>
-      <c r="E38" s="29">
+      <c r="E38" s="27">
         <v>46108</v>
       </c>
       <c r="F38" s="5"/>
-      <c r="H38" s="22">
+      <c r="H38">
         <f>D38-VLOOKUP(A38,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I38" s="28">
+      <c r="I38">
         <f>E38-VLOOKUP(A38,'26035'!A:F,5,0)</f>
         <v>-31</v>
       </c>
-      <c r="J38" s="22">
+      <c r="J38">
         <f>F38-VLOOKUP(A38,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -10982,19 +10983,19 @@
       <c r="D39" s="6">
         <v>46139</v>
       </c>
-      <c r="E39" s="29">
+      <c r="E39" s="27">
         <v>46108</v>
       </c>
       <c r="F39" s="5"/>
-      <c r="H39" s="22">
+      <c r="H39">
         <f>D39-VLOOKUP(A39,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I39" s="28">
+      <c r="I39">
         <f>E39-VLOOKUP(A39,'26035'!A:F,5,0)</f>
         <v>-31</v>
       </c>
-      <c r="J39" s="22">
+      <c r="J39">
         <f>F39-VLOOKUP(A39,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -11012,19 +11013,19 @@
       <c r="D40" s="6">
         <v>46139</v>
       </c>
-      <c r="E40" s="29">
+      <c r="E40" s="27">
         <v>46108</v>
       </c>
       <c r="F40" s="5"/>
-      <c r="H40" s="22">
+      <c r="H40">
         <f>D40-VLOOKUP(A40,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I40" s="28">
+      <c r="I40">
         <f>E40-VLOOKUP(A40,'26035'!A:F,5,0)</f>
         <v>-31</v>
       </c>
-      <c r="J40" s="22">
+      <c r="J40">
         <f>F40-VLOOKUP(A40,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -11042,19 +11043,19 @@
       <c r="D41" s="6">
         <v>46139</v>
       </c>
-      <c r="E41" s="29">
+      <c r="E41" s="27">
         <v>46108</v>
       </c>
       <c r="F41" s="5"/>
-      <c r="H41" s="22">
+      <c r="H41">
         <f>D41-VLOOKUP(A41,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I41" s="28">
+      <c r="I41">
         <f>E41-VLOOKUP(A41,'26035'!A:F,5,0)</f>
         <v>-31</v>
       </c>
-      <c r="J41" s="22">
+      <c r="J41">
         <f>F41-VLOOKUP(A41,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -11072,19 +11073,19 @@
       <c r="D42" s="6">
         <v>46139</v>
       </c>
-      <c r="E42" s="29">
+      <c r="E42" s="27">
         <v>46108</v>
       </c>
       <c r="F42" s="5"/>
-      <c r="H42" s="22">
+      <c r="H42">
         <f>D42-VLOOKUP(A42,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I42" s="28">
+      <c r="I42">
         <f>E42-VLOOKUP(A42,'26035'!A:F,5,0)</f>
         <v>-31</v>
       </c>
-      <c r="J42" s="22">
+      <c r="J42">
         <f>F42-VLOOKUP(A42,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -11102,22 +11103,22 @@
       <c r="D43" s="6">
         <v>46149</v>
       </c>
-      <c r="E43" s="29">
+      <c r="E43" s="27">
         <v>46108</v>
       </c>
       <c r="F43" s="5"/>
       <c r="G43" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="H43" s="22">
+      <c r="H43">
         <f>D43-VLOOKUP(A43,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I43" s="28">
+      <c r="I43">
         <f>E43-VLOOKUP(A43,'26035'!A:F,5,0)</f>
         <v>-39</v>
       </c>
-      <c r="J43" s="22">
+      <c r="J43">
         <f>F43-VLOOKUP(A43,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -11135,19 +11136,19 @@
       <c r="D44" s="9">
         <v>46147</v>
       </c>
-      <c r="E44" s="30">
+      <c r="E44" s="28">
         <v>46108</v>
       </c>
       <c r="F44" s="8"/>
-      <c r="H44" s="22">
+      <c r="H44">
         <f>D44-VLOOKUP(A44,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I44" s="28">
+      <c r="I44">
         <f>E44-VLOOKUP(A44,'26035'!A:F,5,0)</f>
         <v>-39</v>
       </c>
-      <c r="J44" s="22">
+      <c r="J44">
         <f>F44-VLOOKUP(A44,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -11165,19 +11166,19 @@
       <c r="D45" s="6">
         <v>46147</v>
       </c>
-      <c r="E45" s="29">
+      <c r="E45" s="27">
         <v>46108</v>
       </c>
       <c r="F45" s="5"/>
-      <c r="H45" s="22">
+      <c r="H45">
         <f>D45-VLOOKUP(A45,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I45" s="22">
+      <c r="I45">
         <f>E45-VLOOKUP(A45,'26035'!A:F,5,0)</f>
         <v>-39</v>
       </c>
-      <c r="J45" s="22">
+      <c r="J45">
         <f>F45-VLOOKUP(A45,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -11195,19 +11196,19 @@
       <c r="D46" s="6">
         <v>46147</v>
       </c>
-      <c r="E46" s="29">
+      <c r="E46" s="27">
         <v>46108</v>
       </c>
       <c r="F46" s="5"/>
-      <c r="H46" s="22">
+      <c r="H46">
         <f>D46-VLOOKUP(A46,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I46" s="22">
+      <c r="I46">
         <f>E46-VLOOKUP(A46,'26035'!A:F,5,0)</f>
         <v>-39</v>
       </c>
-      <c r="J46" s="22">
+      <c r="J46">
         <f>F46-VLOOKUP(A46,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -11225,50 +11226,50 @@
       <c r="D47" s="6">
         <v>46147</v>
       </c>
-      <c r="E47" s="29">
+      <c r="E47" s="27">
         <v>46108</v>
       </c>
       <c r="F47" s="5"/>
-      <c r="H47" s="22">
+      <c r="H47">
         <f>D47-VLOOKUP(A47,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I47" s="22">
+      <c r="I47">
         <f>E47-VLOOKUP(A47,'26035'!A:F,5,0)</f>
         <v>-39</v>
       </c>
-      <c r="J47" s="22">
+      <c r="J47">
         <f>F47-VLOOKUP(A47,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="24" t="s">
+      <c r="A48" s="23" t="s">
         <v>80</v>
       </c>
-      <c r="B48" s="25" t="s">
+      <c r="B48" s="24" t="s">
         <v>81</v>
       </c>
-      <c r="C48" s="25" t="s">
+      <c r="C48" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="D48" s="26">
+      <c r="D48" s="25">
         <v>46147</v>
       </c>
-      <c r="E48" s="31">
+      <c r="E48" s="29">
         <v>46108</v>
       </c>
-      <c r="F48" s="25"/>
-      <c r="G48" s="27"/>
-      <c r="H48" s="23">
+      <c r="F48" s="24"/>
+      <c r="G48" s="26"/>
+      <c r="H48" s="22">
         <f>D48-VLOOKUP(A48,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I48" s="23">
+      <c r="I48" s="22">
         <f>E48-VLOOKUP(A48,'26035'!A:F,5,0)</f>
         <v>-39</v>
       </c>
-      <c r="J48" s="23">
+      <c r="J48" s="22">
         <f>F48-VLOOKUP(A48,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -11286,19 +11287,19 @@
       <c r="D49" s="6">
         <v>46147</v>
       </c>
-      <c r="E49" s="29">
+      <c r="E49" s="27">
         <v>46108</v>
       </c>
       <c r="F49" s="5"/>
-      <c r="H49" s="22">
+      <c r="H49">
         <f>D49-VLOOKUP(A49,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I49" s="22">
+      <c r="I49">
         <f>E49-VLOOKUP(A49,'26035'!A:F,5,0)</f>
         <v>-39</v>
       </c>
-      <c r="J49" s="22">
+      <c r="J49">
         <f>F49-VLOOKUP(A49,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -11316,19 +11317,19 @@
       <c r="D50" s="6">
         <v>46147</v>
       </c>
-      <c r="E50" s="29">
+      <c r="E50" s="27">
         <v>46108</v>
       </c>
       <c r="F50" s="5"/>
-      <c r="H50" s="22">
+      <c r="H50">
         <f>D50-VLOOKUP(A50,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I50" s="22">
+      <c r="I50">
         <f>E50-VLOOKUP(A50,'26035'!A:F,5,0)</f>
         <v>-39</v>
       </c>
-      <c r="J50" s="22">
+      <c r="J50">
         <f>F50-VLOOKUP(A50,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -11350,15 +11351,15 @@
         <v>46156</v>
       </c>
       <c r="F51" s="5"/>
-      <c r="H51" s="22">
+      <c r="H51">
         <f>D51-VLOOKUP(A51,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I51" s="22">
+      <c r="I51">
         <f>E51-VLOOKUP(A51,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J51" s="22">
+      <c r="J51">
         <f>F51-VLOOKUP(A51,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -11382,15 +11383,15 @@
       <c r="F52" s="6">
         <v>46128</v>
       </c>
-      <c r="H52" s="22">
+      <c r="H52">
         <f>D52-VLOOKUP(A52,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I52" s="22">
+      <c r="I52">
         <f>E52-VLOOKUP(A52,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J52" s="22">
+      <c r="J52">
         <f>F52-VLOOKUP(A52,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -11412,15 +11413,15 @@
         <v>46154</v>
       </c>
       <c r="F53" s="5"/>
-      <c r="H53" s="22">
+      <c r="H53">
         <f>D53-VLOOKUP(A53,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I53" s="22">
+      <c r="I53">
         <f>E53-VLOOKUP(A53,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J53" s="22">
+      <c r="J53">
         <f>F53-VLOOKUP(A53,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -11438,22 +11439,22 @@
       <c r="D54" s="6">
         <v>46156</v>
       </c>
-      <c r="E54" s="31">
+      <c r="E54" s="29">
         <v>46108</v>
       </c>
       <c r="F54" s="5"/>
       <c r="G54" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="H54" s="22">
+      <c r="H54">
         <f>D54-VLOOKUP(A54,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I54" s="23">
+      <c r="I54" s="22">
         <f>E54-VLOOKUP(A54,'26035'!A:F,5,0)</f>
         <v>-48</v>
       </c>
-      <c r="J54" s="22">
+      <c r="J54">
         <f>F54-VLOOKUP(A54,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -11471,22 +11472,22 @@
       <c r="D55" s="6">
         <v>46165</v>
       </c>
-      <c r="E55" s="31">
+      <c r="E55" s="29">
         <v>46108</v>
       </c>
       <c r="F55" s="5"/>
       <c r="G55" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="H55" s="22">
+      <c r="H55">
         <f>D55-VLOOKUP(A55,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I55" s="23">
+      <c r="I55" s="22">
         <f>E55-VLOOKUP(A55,'26035'!A:F,5,0)</f>
         <v>-57</v>
       </c>
-      <c r="J55" s="22">
+      <c r="J55">
         <f>F55-VLOOKUP(A55,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -11504,22 +11505,22 @@
       <c r="D56" s="6">
         <v>46167</v>
       </c>
-      <c r="E56" s="29">
+      <c r="E56" s="27">
         <v>46108</v>
       </c>
       <c r="F56" s="5"/>
       <c r="G56" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="H56" s="22">
+      <c r="H56">
         <f>D56-VLOOKUP(A56,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I56" s="22">
+      <c r="I56">
         <f>E56-VLOOKUP(A56,'26035'!A:F,5,0)</f>
         <v>-59</v>
       </c>
-      <c r="J56" s="22">
+      <c r="J56">
         <f>F56-VLOOKUP(A56,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -11541,15 +11542,15 @@
         <v>46171</v>
       </c>
       <c r="F57" s="5"/>
-      <c r="H57" s="22">
+      <c r="H57">
         <f>D57-VLOOKUP(A57,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I57" s="22">
+      <c r="I57">
         <f>E57-VLOOKUP(A57,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J57" s="22">
+      <c r="J57">
         <f>F57-VLOOKUP(A57,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -11571,15 +11572,15 @@
         <v>46096</v>
       </c>
       <c r="F58" s="11"/>
-      <c r="H58" s="22">
+      <c r="H58">
         <f>D58-VLOOKUP(A58,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I58" s="22">
+      <c r="I58">
         <f>E58-VLOOKUP(A58,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J58" s="22">
+      <c r="J58">
         <f>F58-VLOOKUP(A58,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -11592,7 +11593,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F242D9E7-D647-4506-B36E-32D4E1FC894D}">
-  <sheetPr>
+  <sheetPr codeName="Sheet7">
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
   <dimension ref="A1:J58"/>
@@ -11605,8 +11606,8 @@
     <col min="5" max="5" width="21.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="17.42578125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.42578125" style="13" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.5703125" style="22" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="11.85546875" style="22" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="11.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -11631,13 +11632,13 @@
       <c r="G1" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="H1" s="22" t="s">
+      <c r="H1" t="s">
         <v>110</v>
       </c>
-      <c r="I1" s="22" t="s">
+      <c r="I1" t="s">
         <v>111</v>
       </c>
-      <c r="J1" s="22" t="s">
+      <c r="J1" t="s">
         <v>112</v>
       </c>
     </row>
@@ -11658,15 +11659,15 @@
         <v>46089</v>
       </c>
       <c r="F2" s="20"/>
-      <c r="H2" s="22">
+      <c r="H2">
         <f>D2-VLOOKUP(A2,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I2" s="22">
+      <c r="I2">
         <f>E2-VLOOKUP(A2,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J2" s="22">
+      <c r="J2">
         <f>F2-VLOOKUP(A2,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -11688,15 +11689,15 @@
         <v>46094</v>
       </c>
       <c r="F3" s="5"/>
-      <c r="H3" s="22">
+      <c r="H3">
         <f>D3-VLOOKUP(A3,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I3" s="22">
+      <c r="I3">
         <f>E3-VLOOKUP(A3,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J3" s="22">
+      <c r="J3">
         <f>F3-VLOOKUP(A3,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -11723,45 +11724,45 @@
       <c r="G4" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="H4" s="22">
+      <c r="H4">
         <f>D4-VLOOKUP(A4,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I4" s="22">
+      <c r="I4">
         <f>E4-VLOOKUP(A4,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J4" s="22">
+      <c r="J4">
         <f>F4-VLOOKUP(A4,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="32">
+      <c r="A5" s="30">
         <v>5</v>
       </c>
-      <c r="B5" s="33" t="s">
+      <c r="B5" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="33" t="s">
+      <c r="C5" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="34">
+      <c r="D5" s="32">
         <v>46103</v>
       </c>
-      <c r="E5" s="34">
+      <c r="E5" s="32">
         <v>46103</v>
       </c>
-      <c r="F5" s="33"/>
-      <c r="H5" s="22">
+      <c r="F5" s="31"/>
+      <c r="H5">
         <f>D5-VLOOKUP(A5,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I5" s="22">
+      <c r="I5">
         <f>E5-VLOOKUP(A5,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J5" s="22">
+      <c r="J5">
         <f>F5-VLOOKUP(A5,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -11783,15 +11784,15 @@
         <v>46107</v>
       </c>
       <c r="F6" s="5"/>
-      <c r="H6" s="22">
+      <c r="H6">
         <f>D6-VLOOKUP(A6,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I6" s="22">
+      <c r="I6">
         <f>E6-VLOOKUP(A6,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J6" s="22">
+      <c r="J6">
         <f>F6-VLOOKUP(A6,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -11813,15 +11814,15 @@
         <v>46114</v>
       </c>
       <c r="F7" s="5"/>
-      <c r="H7" s="22">
+      <c r="H7">
         <f>D7-VLOOKUP(A7,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I7" s="22">
+      <c r="I7">
         <f>E7-VLOOKUP(A7,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J7" s="22">
+      <c r="J7">
         <f>F7-VLOOKUP(A7,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -11843,15 +11844,15 @@
         <v>46109</v>
       </c>
       <c r="F8" s="5"/>
-      <c r="H8" s="22">
+      <c r="H8">
         <f>D8-VLOOKUP(A8,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I8" s="22">
+      <c r="I8">
         <f>E8-VLOOKUP(A8,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J8" s="22">
+      <c r="J8">
         <f>F8-VLOOKUP(A8,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -11873,15 +11874,15 @@
         <v>46109</v>
       </c>
       <c r="F9" s="5"/>
-      <c r="H9" s="22">
+      <c r="H9">
         <f>D9-VLOOKUP(A9,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I9" s="22">
+      <c r="I9">
         <f>E9-VLOOKUP(A9,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J9" s="22">
+      <c r="J9">
         <f>F9-VLOOKUP(A9,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -11903,15 +11904,15 @@
         <v>46109</v>
       </c>
       <c r="F10" s="5"/>
-      <c r="H10" s="22">
+      <c r="H10">
         <f>D10-VLOOKUP(A10,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I10" s="22">
+      <c r="I10">
         <f>E10-VLOOKUP(A10,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J10" s="22">
+      <c r="J10">
         <f>F10-VLOOKUP(A10,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -11933,15 +11934,15 @@
         <v>46109</v>
       </c>
       <c r="F11" s="5"/>
-      <c r="H11" s="22">
+      <c r="H11">
         <f>D11-VLOOKUP(A11,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I11" s="22">
+      <c r="I11">
         <f>E11-VLOOKUP(A11,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J11" s="22">
+      <c r="J11">
         <f>F11-VLOOKUP(A11,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -11963,15 +11964,15 @@
         <v>46109</v>
       </c>
       <c r="F12" s="5"/>
-      <c r="H12" s="22">
+      <c r="H12">
         <f>D12-VLOOKUP(A12,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I12" s="22">
+      <c r="I12">
         <f>E12-VLOOKUP(A12,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J12" s="22">
+      <c r="J12">
         <f>F12-VLOOKUP(A12,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -11993,15 +11994,15 @@
         <v>46109</v>
       </c>
       <c r="F13" s="5"/>
-      <c r="H13" s="22">
+      <c r="H13">
         <f>D13-VLOOKUP(A13,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I13" s="22">
+      <c r="I13">
         <f>E13-VLOOKUP(A13,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J13" s="22">
+      <c r="J13">
         <f>F13-VLOOKUP(A13,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -12023,15 +12024,15 @@
         <v>46109</v>
       </c>
       <c r="F14" s="5"/>
-      <c r="H14" s="22">
+      <c r="H14">
         <f>D14-VLOOKUP(A14,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I14" s="22">
+      <c r="I14">
         <f>E14-VLOOKUP(A14,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J14" s="22">
+      <c r="J14">
         <f>F14-VLOOKUP(A14,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -12053,15 +12054,15 @@
         <v>46109</v>
       </c>
       <c r="F15" s="5"/>
-      <c r="H15" s="22">
+      <c r="H15">
         <f>D15-VLOOKUP(A15,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I15" s="22">
+      <c r="I15">
         <f>E15-VLOOKUP(A15,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J15" s="22">
+      <c r="J15">
         <f>F15-VLOOKUP(A15,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -12083,15 +12084,15 @@
         <v>46108</v>
       </c>
       <c r="F16" s="5"/>
-      <c r="H16" s="22">
+      <c r="H16">
         <f>D16-VLOOKUP(A16,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I16" s="22">
+      <c r="I16">
         <f>E16-VLOOKUP(A16,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J16" s="22">
+      <c r="J16">
         <f>F16-VLOOKUP(A16,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -12113,15 +12114,15 @@
         <v>46109</v>
       </c>
       <c r="F17" s="5"/>
-      <c r="H17" s="22">
+      <c r="H17">
         <f>D17-VLOOKUP(A17,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I17" s="22">
+      <c r="I17">
         <f>E17-VLOOKUP(A17,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J17" s="22">
+      <c r="J17">
         <f>F17-VLOOKUP(A17,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -12143,15 +12144,15 @@
         <v>46115</v>
       </c>
       <c r="F18" s="5"/>
-      <c r="H18" s="22">
+      <c r="H18">
         <f>D18-VLOOKUP(A18,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I18" s="22">
+      <c r="I18">
         <f>E18-VLOOKUP(A18,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J18" s="22">
+      <c r="J18">
         <f>F18-VLOOKUP(A18,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -12176,15 +12177,15 @@
       <c r="G19" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="H19" s="22">
+      <c r="H19">
         <f>D19-VLOOKUP(A19,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I19" s="22">
+      <c r="I19">
         <f>E19-VLOOKUP(A19,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J19" s="22">
+      <c r="J19">
         <f>F19-VLOOKUP(A19,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -12206,15 +12207,15 @@
         <v>46108</v>
       </c>
       <c r="F20" s="5"/>
-      <c r="H20" s="22">
+      <c r="H20">
         <f>D20-VLOOKUP(A20,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I20" s="22">
+      <c r="I20">
         <f>E20-VLOOKUP(A20,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J20" s="22">
+      <c r="J20">
         <f>F20-VLOOKUP(A20,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -12236,15 +12237,15 @@
         <v>46108</v>
       </c>
       <c r="F21" s="5"/>
-      <c r="H21" s="22">
+      <c r="H21">
         <f>D21-VLOOKUP(A21,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I21" s="22">
+      <c r="I21">
         <f>E21-VLOOKUP(A21,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J21" s="22">
+      <c r="J21">
         <f>F21-VLOOKUP(A21,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -12266,15 +12267,15 @@
         <v>46108</v>
       </c>
       <c r="F22" s="5"/>
-      <c r="H22" s="22">
+      <c r="H22">
         <f>D22-VLOOKUP(A22,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I22" s="22">
+      <c r="I22">
         <f>E22-VLOOKUP(A22,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J22" s="22">
+      <c r="J22">
         <f>F22-VLOOKUP(A22,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -12296,15 +12297,15 @@
         <v>46108</v>
       </c>
       <c r="F23" s="5"/>
-      <c r="H23" s="22">
+      <c r="H23">
         <f>D23-VLOOKUP(A23,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I23" s="22">
+      <c r="I23">
         <f>E23-VLOOKUP(A23,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J23" s="22">
+      <c r="J23">
         <f>F23-VLOOKUP(A23,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -12326,15 +12327,15 @@
         <v>46108</v>
       </c>
       <c r="F24" s="5"/>
-      <c r="H24" s="22">
+      <c r="H24">
         <f>D24-VLOOKUP(A24,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I24" s="22">
+      <c r="I24">
         <f>E24-VLOOKUP(A24,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J24" s="22">
+      <c r="J24">
         <f>F24-VLOOKUP(A24,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -12356,15 +12357,15 @@
         <v>46108</v>
       </c>
       <c r="F25" s="5"/>
-      <c r="H25" s="22">
+      <c r="H25">
         <f>D25-VLOOKUP(A25,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I25" s="22">
+      <c r="I25">
         <f>E25-VLOOKUP(A25,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J25" s="22">
+      <c r="J25">
         <f>F25-VLOOKUP(A25,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -12386,15 +12387,15 @@
         <v>46104</v>
       </c>
       <c r="F26" s="5"/>
-      <c r="H26" s="22">
+      <c r="H26">
         <f>D26-VLOOKUP(A26,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I26" s="22">
+      <c r="I26">
         <f>E26-VLOOKUP(A26,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J26" s="22">
+      <c r="J26">
         <f>F26-VLOOKUP(A26,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -12416,15 +12417,15 @@
         <v>46113</v>
       </c>
       <c r="F27" s="5"/>
-      <c r="H27" s="22">
+      <c r="H27">
         <f>D27-VLOOKUP(A27,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I27" s="22">
+      <c r="I27">
         <f>E27-VLOOKUP(A27,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J27" s="22">
+      <c r="J27">
         <f>F27-VLOOKUP(A27,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -12446,15 +12447,15 @@
         <v>46114</v>
       </c>
       <c r="F28" s="5"/>
-      <c r="H28" s="22">
+      <c r="H28">
         <f>D28-VLOOKUP(A28,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I28" s="22">
+      <c r="I28">
         <f>E28-VLOOKUP(A28,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J28" s="22">
+      <c r="J28">
         <f>F28-VLOOKUP(A28,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -12476,15 +12477,15 @@
         <v>46118</v>
       </c>
       <c r="F29" s="5"/>
-      <c r="H29" s="22">
+      <c r="H29">
         <f>D29-VLOOKUP(A29,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I29" s="22">
+      <c r="I29">
         <f>E29-VLOOKUP(A29,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J29" s="22">
+      <c r="J29">
         <f>F29-VLOOKUP(A29,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -12506,15 +12507,15 @@
         <v>46124</v>
       </c>
       <c r="F30" s="5"/>
-      <c r="H30" s="22">
+      <c r="H30">
         <f>D30-VLOOKUP(A30,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I30" s="22">
+      <c r="I30">
         <f>E30-VLOOKUP(A30,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J30" s="22">
+      <c r="J30">
         <f>F30-VLOOKUP(A30,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -12536,15 +12537,15 @@
         <v>46137</v>
       </c>
       <c r="F31" s="5"/>
-      <c r="H31" s="22">
+      <c r="H31">
         <f>D31-VLOOKUP(A31,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I31" s="22">
+      <c r="I31">
         <f>E31-VLOOKUP(A31,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J31" s="22">
+      <c r="J31">
         <f>F31-VLOOKUP(A31,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -12571,15 +12572,15 @@
       <c r="G32" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="H32" s="22">
+      <c r="H32">
         <f>D32-VLOOKUP(A32,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I32" s="28">
+      <c r="I32">
         <f>E32-VLOOKUP(A32,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J32" s="22">
+      <c r="J32">
         <f>F32-VLOOKUP(A32,'26035'!A:F,6,0)</f>
         <v>46127</v>
       </c>
@@ -12604,15 +12605,15 @@
       <c r="G33" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="H33" s="22">
+      <c r="H33">
         <f>D33-VLOOKUP(A33,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I33" s="28">
+      <c r="I33">
         <f>E33-VLOOKUP(A33,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J33" s="22">
+      <c r="J33">
         <f>F33-VLOOKUP(A33,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -12637,15 +12638,15 @@
       <c r="G34" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="H34" s="22">
+      <c r="H34">
         <f>D34-VLOOKUP(A34,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I34" s="28">
+      <c r="I34">
         <f>E34-VLOOKUP(A34,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J34" s="22">
+      <c r="J34">
         <f>F34-VLOOKUP(A34,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -12667,15 +12668,15 @@
         <v>46143</v>
       </c>
       <c r="F35" s="5"/>
-      <c r="H35" s="22">
+      <c r="H35">
         <f>D35-VLOOKUP(A35,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I35" s="28">
+      <c r="I35">
         <f>E35-VLOOKUP(A35,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J35" s="22">
+      <c r="J35">
         <f>F35-VLOOKUP(A35,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -12700,15 +12701,15 @@
       <c r="G36" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="H36" s="22">
+      <c r="H36">
         <f>D36-VLOOKUP(A36,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I36" s="28">
+      <c r="I36">
         <f>E36-VLOOKUP(A36,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J36" s="22">
+      <c r="J36">
         <f>F36-VLOOKUP(A36,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -12730,15 +12731,15 @@
         <v>46139</v>
       </c>
       <c r="F37" s="5"/>
-      <c r="H37" s="22">
+      <c r="H37">
         <f>D37-VLOOKUP(A37,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I37" s="28">
+      <c r="I37">
         <f>E37-VLOOKUP(A37,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J37" s="22">
+      <c r="J37">
         <f>F37-VLOOKUP(A37,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -12760,15 +12761,15 @@
         <v>46139</v>
       </c>
       <c r="F38" s="5"/>
-      <c r="H38" s="22">
+      <c r="H38">
         <f>D38-VLOOKUP(A38,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I38" s="28">
+      <c r="I38">
         <f>E38-VLOOKUP(A38,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J38" s="22">
+      <c r="J38">
         <f>F38-VLOOKUP(A38,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -12790,15 +12791,15 @@
         <v>46139</v>
       </c>
       <c r="F39" s="5"/>
-      <c r="H39" s="22">
+      <c r="H39">
         <f>D39-VLOOKUP(A39,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I39" s="28">
+      <c r="I39">
         <f>E39-VLOOKUP(A39,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J39" s="22">
+      <c r="J39">
         <f>F39-VLOOKUP(A39,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -12820,15 +12821,15 @@
         <v>46139</v>
       </c>
       <c r="F40" s="5"/>
-      <c r="H40" s="22">
+      <c r="H40">
         <f>D40-VLOOKUP(A40,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I40" s="28">
+      <c r="I40">
         <f>E40-VLOOKUP(A40,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J40" s="22">
+      <c r="J40">
         <f>F40-VLOOKUP(A40,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -12850,15 +12851,15 @@
         <v>46139</v>
       </c>
       <c r="F41" s="5"/>
-      <c r="H41" s="22">
+      <c r="H41">
         <f>D41-VLOOKUP(A41,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I41" s="28">
+      <c r="I41">
         <f>E41-VLOOKUP(A41,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J41" s="22">
+      <c r="J41">
         <f>F41-VLOOKUP(A41,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -12880,15 +12881,15 @@
         <v>46139</v>
       </c>
       <c r="F42" s="5"/>
-      <c r="H42" s="22">
+      <c r="H42">
         <f>D42-VLOOKUP(A42,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I42" s="28">
+      <c r="I42">
         <f>E42-VLOOKUP(A42,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J42" s="22">
+      <c r="J42">
         <f>F42-VLOOKUP(A42,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -12913,15 +12914,15 @@
       <c r="G43" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="H43" s="22">
+      <c r="H43">
         <f>D43-VLOOKUP(A43,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I43" s="28">
+      <c r="I43">
         <f>E43-VLOOKUP(A43,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J43" s="22">
+      <c r="J43">
         <f>F43-VLOOKUP(A43,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -12943,15 +12944,15 @@
         <v>46147</v>
       </c>
       <c r="F44" s="8"/>
-      <c r="H44" s="22">
+      <c r="H44">
         <f>D44-VLOOKUP(A44,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I44" s="28">
+      <c r="I44">
         <f>E44-VLOOKUP(A44,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J44" s="22">
+      <c r="J44">
         <f>F44-VLOOKUP(A44,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -12973,15 +12974,15 @@
         <v>46147</v>
       </c>
       <c r="F45" s="5"/>
-      <c r="H45" s="22">
+      <c r="H45">
         <f>D45-VLOOKUP(A45,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I45" s="22">
+      <c r="I45">
         <f>E45-VLOOKUP(A45,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J45" s="22">
+      <c r="J45">
         <f>F45-VLOOKUP(A45,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -13003,15 +13004,15 @@
         <v>46147</v>
       </c>
       <c r="F46" s="5"/>
-      <c r="H46" s="22">
+      <c r="H46">
         <f>D46-VLOOKUP(A46,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I46" s="22">
+      <c r="I46">
         <f>E46-VLOOKUP(A46,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J46" s="22">
+      <c r="J46">
         <f>F46-VLOOKUP(A46,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -13033,15 +13034,15 @@
         <v>46147</v>
       </c>
       <c r="F47" s="5"/>
-      <c r="H47" s="22">
+      <c r="H47">
         <f>D47-VLOOKUP(A47,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I47" s="22">
+      <c r="I47">
         <f>E47-VLOOKUP(A47,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J47" s="22">
+      <c r="J47">
         <f>F47-VLOOKUP(A47,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -13063,15 +13064,15 @@
         <v>46147</v>
       </c>
       <c r="F48" s="5"/>
-      <c r="H48" s="22">
+      <c r="H48">
         <f>D48-VLOOKUP(A48,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I48" s="22">
+      <c r="I48">
         <f>E48-VLOOKUP(A48,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J48" s="22">
+      <c r="J48">
         <f>F48-VLOOKUP(A48,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -13093,15 +13094,15 @@
         <v>46147</v>
       </c>
       <c r="F49" s="5"/>
-      <c r="H49" s="22">
+      <c r="H49">
         <f>D49-VLOOKUP(A49,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I49" s="22">
+      <c r="I49">
         <f>E49-VLOOKUP(A49,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J49" s="22">
+      <c r="J49">
         <f>F49-VLOOKUP(A49,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -13123,15 +13124,15 @@
         <v>46147</v>
       </c>
       <c r="F50" s="5"/>
-      <c r="H50" s="22">
+      <c r="H50">
         <f>D50-VLOOKUP(A50,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I50" s="22">
+      <c r="I50">
         <f>E50-VLOOKUP(A50,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J50" s="22">
+      <c r="J50">
         <f>F50-VLOOKUP(A50,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -13153,15 +13154,15 @@
         <v>46156</v>
       </c>
       <c r="F51" s="5"/>
-      <c r="H51" s="22">
+      <c r="H51">
         <f>D51-VLOOKUP(A51,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I51" s="22">
+      <c r="I51">
         <f>E51-VLOOKUP(A51,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J51" s="22">
+      <c r="J51">
         <f>F51-VLOOKUP(A51,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -13185,15 +13186,15 @@
       <c r="F52" s="6">
         <v>46128</v>
       </c>
-      <c r="H52" s="22">
+      <c r="H52">
         <f>D52-VLOOKUP(A52,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I52" s="22">
+      <c r="I52">
         <f>E52-VLOOKUP(A52,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J52" s="22">
+      <c r="J52">
         <f>F52-VLOOKUP(A52,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -13215,15 +13216,15 @@
         <v>46154</v>
       </c>
       <c r="F53" s="5"/>
-      <c r="H53" s="22">
+      <c r="H53">
         <f>D53-VLOOKUP(A53,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I53" s="22">
+      <c r="I53">
         <f>E53-VLOOKUP(A53,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J53" s="22">
+      <c r="J53">
         <f>F53-VLOOKUP(A53,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -13248,15 +13249,15 @@
       <c r="G54" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="H54" s="22">
+      <c r="H54">
         <f>D54-VLOOKUP(A54,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I54" s="22">
+      <c r="I54">
         <f>E54-VLOOKUP(A54,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J54" s="22">
+      <c r="J54">
         <f>F54-VLOOKUP(A54,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -13281,15 +13282,15 @@
       <c r="G55" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="H55" s="22">
+      <c r="H55">
         <f>D55-VLOOKUP(A55,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I55" s="22">
+      <c r="I55">
         <f>E55-VLOOKUP(A55,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J55" s="22">
+      <c r="J55">
         <f>F55-VLOOKUP(A55,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -13314,15 +13315,15 @@
       <c r="G56" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="H56" s="22">
+      <c r="H56">
         <f>D56-VLOOKUP(A56,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I56" s="22">
+      <c r="I56">
         <f>E56-VLOOKUP(A56,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J56" s="22">
+      <c r="J56">
         <f>F56-VLOOKUP(A56,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -13344,15 +13345,15 @@
         <v>46171</v>
       </c>
       <c r="F57" s="5"/>
-      <c r="H57" s="22">
+      <c r="H57">
         <f>D57-VLOOKUP(A57,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I57" s="22">
+      <c r="I57">
         <f>E57-VLOOKUP(A57,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J57" s="22">
+      <c r="J57">
         <f>F57-VLOOKUP(A57,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
@@ -13374,15 +13375,15 @@
         <v>46096</v>
       </c>
       <c r="F58" s="11"/>
-      <c r="H58" s="22">
+      <c r="H58">
         <f>D58-VLOOKUP(A58,'26035'!A:F,4,0)</f>
         <v>0</v>
       </c>
-      <c r="I58" s="22">
+      <c r="I58">
         <f>E58-VLOOKUP(A58,'26035'!A:F,5,0)</f>
         <v>0</v>
       </c>
-      <c r="J58" s="22">
+      <c r="J58">
         <f>F58-VLOOKUP(A58,'26035'!A:F,6,0)</f>
         <v>0</v>
       </c>
